--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEE7872-33E7-42BD-9D0D-3ED779FBD883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE049EB-54B6-486C-8A48-9B6D23803C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="500">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1967,6 +1967,70 @@
   </si>
   <si>
     <t>사테</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.05.13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연합팀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CK/PL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지동원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파도튜브</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박준오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수범</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사테</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배성흠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김범수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박성준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜냐맨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박성균</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구성훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>민찬기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2061,10 +2125,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2383,7 +2447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0780BE45-9F1A-41AD-B87B-A1A571694506}">
-  <dimension ref="A1:R917"/>
+  <dimension ref="A1:R924"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="10.1875" bestFit="1" customWidth="1"/>
@@ -2440,7 +2504,7 @@
       <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>436</v>
       </c>
       <c r="P1" t="s">
@@ -8983,16 +9047,16 @@
         <v>패</v>
       </c>
       <c r="E255">
-        <f>COUNTIF(M255:M261,"승")</f>
+        <f>COUNTIF(M255:M262,"승")</f>
         <v>3</v>
       </c>
       <c r="F255">
-        <f>COUNTA(M255:M261)-E255</f>
-        <v>4</v>
+        <f>COUNTA(M255:M262)-E255</f>
+        <v>5</v>
       </c>
       <c r="G255" s="1">
         <f>E255/(E255+F255)</f>
-        <v>0.42857142857142855</v>
+        <v>0.375</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>177</v>
@@ -24696,7 +24760,7 @@
         <v>37</v>
       </c>
       <c r="L899" t="str">
-        <f t="shared" ref="L899:L917" si="14">INDEX($R$2:$R$99,MATCH(K899,$Q$2:$Q$99,0))</f>
+        <f t="shared" ref="L899:L924" si="14">INDEX($R$2:$R$99,MATCH(K899,$Q$2:$Q$99,0))</f>
         <v>Z</v>
       </c>
       <c r="M899" t="s">
@@ -24954,19 +25018,19 @@
       </c>
       <c r="D910" t="str">
         <f>IF(E910&gt;F910,"승",IF(E910&lt;F910,"패"))</f>
-        <v>승</v>
+        <v>패</v>
       </c>
       <c r="E910">
-        <f>COUNTIF(M910:M914,"승")</f>
+        <f>COUNTIF(M910:M917,"승")</f>
         <v>3</v>
       </c>
       <c r="F910">
-        <f>COUNTA(M910:M914)-E910</f>
-        <v>2</v>
+        <f>COUNTA(M910:M917)-E910</f>
+        <v>5</v>
       </c>
       <c r="G910" s="1">
         <f>E910/(E910+F910)</f>
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="H910" s="1" t="s">
         <v>120</v>
@@ -25033,7 +25097,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="913" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="913" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I913" s="2">
         <v>4</v>
       </c>
@@ -25054,7 +25118,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="914" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="914" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I914" s="2">
         <v>5</v>
       </c>
@@ -25075,7 +25139,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="915" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="915" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I915" s="2">
         <v>6</v>
       </c>
@@ -25096,7 +25160,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="916" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="916" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I916" s="2">
         <v>7</v>
       </c>
@@ -25117,7 +25181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="917" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="917" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I917" s="2">
         <v>8</v>
       </c>
@@ -25136,6 +25200,178 @@
       </c>
       <c r="N917" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="918" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A918" t="s">
+        <v>484</v>
+      </c>
+      <c r="B918" t="s">
+        <v>485</v>
+      </c>
+      <c r="C918" t="s">
+        <v>486</v>
+      </c>
+      <c r="D918" t="str">
+        <f>IF(E918&gt;F918,"승",IF(E918&lt;F918,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E918">
+        <f>COUNTIF(M918:M924,"승")</f>
+        <v>2</v>
+      </c>
+      <c r="F918">
+        <f>COUNTA(M918:M924)-E918</f>
+        <v>5</v>
+      </c>
+      <c r="G918" s="1">
+        <f>E918/(E918+F918)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I918">
+        <v>1</v>
+      </c>
+      <c r="J918">
+        <v>1</v>
+      </c>
+      <c r="K918" t="s">
+        <v>487</v>
+      </c>
+      <c r="L918" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="M918" t="s">
+        <v>4</v>
+      </c>
+      <c r="N918" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I919">
+        <v>2</v>
+      </c>
+      <c r="J919">
+        <v>2</v>
+      </c>
+      <c r="K919" t="s">
+        <v>488</v>
+      </c>
+      <c r="L919" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="M919" t="s">
+        <v>4</v>
+      </c>
+      <c r="N919" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="920" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I920">
+        <v>3</v>
+      </c>
+      <c r="J920">
+        <v>3</v>
+      </c>
+      <c r="K920" t="s">
+        <v>37</v>
+      </c>
+      <c r="L920" t="str">
+        <f t="shared" si="14"/>
+        <v>Z</v>
+      </c>
+      <c r="M920" t="s">
+        <v>3</v>
+      </c>
+      <c r="N920" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="921" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I921">
+        <v>4</v>
+      </c>
+      <c r="J921">
+        <v>4</v>
+      </c>
+      <c r="K921" t="s">
+        <v>489</v>
+      </c>
+      <c r="L921" t="str">
+        <f t="shared" si="14"/>
+        <v>Z</v>
+      </c>
+      <c r="M921" t="s">
+        <v>4</v>
+      </c>
+      <c r="N921" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="922" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I922">
+        <v>5</v>
+      </c>
+      <c r="J922">
+        <v>5</v>
+      </c>
+      <c r="K922" t="s">
+        <v>490</v>
+      </c>
+      <c r="L922" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="M922" t="s">
+        <v>3</v>
+      </c>
+      <c r="N922" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="923" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I923">
+        <v>6</v>
+      </c>
+      <c r="J923">
+        <v>6</v>
+      </c>
+      <c r="K923" t="s">
+        <v>491</v>
+      </c>
+      <c r="L923" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="M923" t="s">
+        <v>4</v>
+      </c>
+      <c r="N923" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I924">
+        <v>7</v>
+      </c>
+      <c r="J924">
+        <v>7</v>
+      </c>
+      <c r="K924" t="s">
+        <v>492</v>
+      </c>
+      <c r="L924" t="str">
+        <f t="shared" si="14"/>
+        <v>Z</v>
+      </c>
+      <c r="M924" t="s">
+        <v>4</v>
+      </c>
+      <c r="N924" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -25178,10 +25414,10 @@
       <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B5" s="4">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE049EB-54B6-486C-8A48-9B6D23803C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E592D5-180E-4B2A-9E87-1721985010A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -7532,7 +7532,7 @@
         <v>0.75</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="I192" s="2">
         <v>1</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E592D5-180E-4B2A-9E87-1721985010A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548EAA64-2231-4C0C-9344-BA476C7FF8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="507">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2031,6 +2031,34 @@
   </si>
   <si>
     <t>민찬기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.05.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국팀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수범</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미후</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제이스타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>샤오슈아이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지동원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2447,7 +2475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0780BE45-9F1A-41AD-B87B-A1A571694506}">
-  <dimension ref="A1:R924"/>
+  <dimension ref="A1:R1224"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="10.1875" bestFit="1" customWidth="1"/>
@@ -24760,7 +24788,7 @@
         <v>37</v>
       </c>
       <c r="L899" t="str">
-        <f t="shared" ref="L899:L924" si="14">INDEX($R$2:$R$99,MATCH(K899,$Q$2:$Q$99,0))</f>
+        <f t="shared" ref="L899:L962" si="14">INDEX($R$2:$R$99,MATCH(K899,$Q$2:$Q$99,0))</f>
         <v>Z</v>
       </c>
       <c r="M899" t="s">
@@ -25372,6 +25400,1951 @@
       </c>
       <c r="N924" t="s">
         <v>499</v>
+      </c>
+    </row>
+    <row r="925" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A925" t="s">
+        <v>500</v>
+      </c>
+      <c r="B925" t="s">
+        <v>501</v>
+      </c>
+      <c r="C925" t="s">
+        <v>173</v>
+      </c>
+      <c r="D925" t="str">
+        <f>IF(E925&gt;F925,"승",IF(E925&lt;F925,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E925">
+        <f>COUNTIF(M925:M932,"승")</f>
+        <v>5</v>
+      </c>
+      <c r="F925">
+        <f>COUNTA(M925:M932)-E925</f>
+        <v>3</v>
+      </c>
+      <c r="G925" s="1">
+        <f>E925/(E925+F925)</f>
+        <v>0.625</v>
+      </c>
+      <c r="I925">
+        <v>1</v>
+      </c>
+      <c r="J925">
+        <v>1</v>
+      </c>
+      <c r="K925" t="s">
+        <v>26</v>
+      </c>
+      <c r="L925" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="M925" t="s">
+        <v>4</v>
+      </c>
+      <c r="N925" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="926" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I926">
+        <v>2</v>
+      </c>
+      <c r="J926">
+        <v>2</v>
+      </c>
+      <c r="K926" t="s">
+        <v>38</v>
+      </c>
+      <c r="L926" t="str">
+        <f t="shared" si="14"/>
+        <v>Z</v>
+      </c>
+      <c r="M926" t="s">
+        <v>3</v>
+      </c>
+      <c r="N926" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="927" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I927">
+        <v>3</v>
+      </c>
+      <c r="J927">
+        <v>3</v>
+      </c>
+      <c r="K927" t="s">
+        <v>26</v>
+      </c>
+      <c r="L927" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="M927" t="s">
+        <v>3</v>
+      </c>
+      <c r="N927" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="I928">
+        <v>4</v>
+      </c>
+      <c r="J928">
+        <v>4</v>
+      </c>
+      <c r="K928" t="s">
+        <v>38</v>
+      </c>
+      <c r="L928" t="str">
+        <f t="shared" si="14"/>
+        <v>Z</v>
+      </c>
+      <c r="M928" t="s">
+        <v>4</v>
+      </c>
+      <c r="N928" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="929" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I929">
+        <v>5</v>
+      </c>
+      <c r="J929">
+        <v>5</v>
+      </c>
+      <c r="K929" t="s">
+        <v>502</v>
+      </c>
+      <c r="L929" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="M929" t="s">
+        <v>3</v>
+      </c>
+      <c r="N929" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="930" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I930">
+        <v>6</v>
+      </c>
+      <c r="J930">
+        <v>6</v>
+      </c>
+      <c r="K930" t="s">
+        <v>502</v>
+      </c>
+      <c r="L930" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="M930" t="s">
+        <v>4</v>
+      </c>
+      <c r="N930" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="931" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I931">
+        <v>7</v>
+      </c>
+      <c r="J931">
+        <v>7</v>
+      </c>
+      <c r="K931" t="s">
+        <v>506</v>
+      </c>
+      <c r="L931" t="str">
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K931,$Q$2:$Q$99,0)),"")</f>
+        <v>T</v>
+      </c>
+      <c r="M931" t="s">
+        <v>3</v>
+      </c>
+      <c r="N931" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="932" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I932">
+        <v>8</v>
+      </c>
+      <c r="J932">
+        <v>8</v>
+      </c>
+      <c r="K932" t="s">
+        <v>506</v>
+      </c>
+      <c r="L932" t="str">
+        <f t="shared" ref="L932:L995" si="15">IFERROR(INDEX($R$2:$R$99,MATCH(K932,$Q$2:$Q$99,0)),"")</f>
+        <v>T</v>
+      </c>
+      <c r="M932" t="s">
+        <v>3</v>
+      </c>
+      <c r="N932" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="933" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L933" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="934" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L934" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="935" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L935" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="936" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L936" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="937" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L937" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="938" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L938" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="939" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L939" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="940" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L940" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="941" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L941" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="942" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L942" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="943" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L943" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="944" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L944" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="945" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L945" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="946" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L946" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="947" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L947" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="948" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L948" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="949" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L949" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="950" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L950" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="951" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L951" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="952" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L952" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="953" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L953" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="954" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L954" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="955" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L955" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="956" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L956" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="957" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L957" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="958" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L958" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="959" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L959" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="960" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L960" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="961" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L961" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="962" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L962" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="963" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L963" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="964" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L964" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="965" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L965" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="966" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L966" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="967" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L967" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="968" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L968" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="969" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L969" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="970" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L970" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="971" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L971" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="972" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L972" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="973" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L973" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="974" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L974" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="975" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L975" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="976" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L976" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="977" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L977" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="978" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L978" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="979" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L979" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="980" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L980" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="981" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L981" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="982" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L982" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="983" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L983" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="984" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L984" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="985" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L985" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="986" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L986" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="987" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L987" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="988" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L988" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="989" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L989" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="990" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L990" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="991" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L991" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="992" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L992" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="993" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L993" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="994" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L994" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="995" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L995" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="996" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L996" t="str">
+        <f t="shared" ref="L996:L1059" si="16">IFERROR(INDEX($R$2:$R$99,MATCH(K996,$Q$2:$Q$99,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="997" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L997" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="998" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L998" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="999" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L999" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1000" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1000" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1001" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1001" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1002" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1002" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1003" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1003" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1004" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1004" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1005" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1005" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1006" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1006" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1007" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1007" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1008" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1008" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1009" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1009" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1010" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1010" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1011" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1011" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1012" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1012" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1013" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1013" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1014" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1014" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1015" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1015" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1016" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1016" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1017" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1017" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1018" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1018" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1019" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1019" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1020" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1020" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1021" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1021" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1022" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1022" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1023" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1023" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1024" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1024" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1025" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1025" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1026" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1026" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1027" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1027" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1028" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1028" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1029" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1029" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1030" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1030" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1031" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1031" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1032" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1032" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1033" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1033" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1034" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1034" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1035" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1035" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1036" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1036" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1037" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1037" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1038" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1038" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1039" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1039" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1040" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1040" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1041" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1041" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1042" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1042" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1043" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1043" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1044" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1044" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1045" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1045" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1046" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1046" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1047" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1047" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1048" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1048" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1049" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1049" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1050" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1050" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1051" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1051" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1052" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1052" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1053" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1053" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1054" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1054" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1055" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1055" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1056" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1056" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1057" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1057" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1058" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1058" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1059" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1059" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1060" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1060" t="str">
+        <f t="shared" ref="L1060:L1123" si="17">IFERROR(INDEX($R$2:$R$99,MATCH(K1060,$Q$2:$Q$99,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1061" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1061" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1062" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1062" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1063" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1063" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1064" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1064" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1065" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1065" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1066" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1066" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1067" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1067" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1068" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1068" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1069" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1069" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1070" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1070" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1071" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1071" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1072" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1072" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1073" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1073" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1074" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1074" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1075" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1075" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1076" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1076" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1077" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1077" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1078" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1078" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1079" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1079" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1080" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1080" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1081" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1081" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1082" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1082" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1083" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1083" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1084" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1084" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1085" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1085" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1086" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1086" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1087" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1087" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1088" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1088" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1089" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1089" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1090" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1090" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1091" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1091" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1092" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1092" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1093" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1093" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1094" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1094" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1095" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1095" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1096" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1096" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1097" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1097" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1098" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1098" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1099" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1099" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1100" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1100" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1101" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1101" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1102" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1102" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1103" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1103" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1104" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1104" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1105" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1105" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1106" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1106" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1107" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1107" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1108" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1108" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1109" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1109" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1110" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1110" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1111" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1111" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1112" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1112" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1113" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1113" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1114" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1114" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1115" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1115" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1116" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1116" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1117" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1117" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1118" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1118" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1119" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1119" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1120" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1120" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1121" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1121" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1122" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1122" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1123" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1123" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1124" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1124" t="str">
+        <f t="shared" ref="L1124:L1187" si="18">IFERROR(INDEX($R$2:$R$99,MATCH(K1124,$Q$2:$Q$99,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1125" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1125" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1126" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1126" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1127" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1127" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1128" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1128" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1129" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1129" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1130" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1130" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1131" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1131" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1132" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1132" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1133" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1133" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1134" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1134" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1135" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1135" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1136" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1136" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1137" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1137" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1138" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1138" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1139" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1139" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1140" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1140" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1141" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1141" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1142" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1142" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1143" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1143" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1144" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1144" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1145" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1145" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1146" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1146" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1147" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1147" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1148" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1148" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1149" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1149" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1150" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1150" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1151" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1151" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1152" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1152" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1153" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1153" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1154" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1154" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1155" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1155" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1156" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1156" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1157" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1157" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1158" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1158" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1159" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1159" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1160" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1160" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1161" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1161" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1162" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1162" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1163" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1163" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1164" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1164" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1165" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1165" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1166" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1166" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1167" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1167" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1168" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1168" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1169" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1169" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1170" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1170" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1171" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1171" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1172" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1172" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1173" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1173" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1174" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1174" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1175" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1175" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1176" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1176" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1177" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1177" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1178" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1178" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1179" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1179" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1180" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1180" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1181" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1181" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1182" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1182" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1183" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1183" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1184" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1184" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1185" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1185" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1186" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1186" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1187" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1187" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1188" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1188" t="str">
+        <f t="shared" ref="L1188:L1224" si="19">IFERROR(INDEX($R$2:$R$99,MATCH(K1188,$Q$2:$Q$99,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1189" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1189" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1190" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1190" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1191" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1191" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1192" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1192" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1193" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1193" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1194" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1194" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1195" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1195" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1196" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1196" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1197" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1197" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1198" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1198" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1199" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1199" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1200" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1200" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1201" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1201" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1202" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1202" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1203" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1203" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1204" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1204" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1205" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1205" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1206" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1206" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1207" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1207" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1208" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1208" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1209" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1209" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1210" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1210" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1211" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1211" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1212" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1212" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1213" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1213" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1214" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1214" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1215" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1215" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1216" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1216" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1217" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1217" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1218" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1218" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1219" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1219" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1220" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1220" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1221" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1221" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1222" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1222" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1223" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1223" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="1224" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="L1224" t="str">
+        <f t="shared" si="19"/>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11D4E05-1CA1-4B46-B156-DD79874E4771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCF6ADA-CC43-4C08-ABED-EB04B1149E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3708" uniqueCount="576">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2248,6 +2248,24 @@
   </si>
   <si>
     <t>[A]</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=EEKHJqX75mK3wQ4q&amp;t=3072</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=wnnzwM2rohdPzBDX&amp;t=5727</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=uncY3jL6C-4AUYd1&amp;t=6300</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=u3SLv6pHIIXXLyXP&amp;t=8085</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=sxZ8coKTaAiHSJcZ&amp;t=9820</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fgJOMAk8DPI?si=s70ZCwQHDvQvYDtU&amp;t=11383</t>
   </si>
 </sst>
 </file>
@@ -3795,8 +3813,8 @@
       <c r="I33" s="2">
         <v>9</v>
       </c>
-      <c r="J33">
-        <v>9</v>
+      <c r="J33" t="s">
+        <v>569</v>
       </c>
       <c r="K33" t="s">
         <v>19</v>
@@ -4087,8 +4105,8 @@
       <c r="I42" s="2">
         <v>9</v>
       </c>
-      <c r="J42">
-        <v>9</v>
+      <c r="J42" t="s">
+        <v>569</v>
       </c>
       <c r="K42" t="s">
         <v>19</v>
@@ -4328,8 +4346,8 @@
       <c r="I51" s="2">
         <v>9</v>
       </c>
-      <c r="J51">
-        <v>9</v>
+      <c r="J51" t="s">
+        <v>569</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
@@ -5397,6 +5415,9 @@
       <c r="N89" t="s">
         <v>120</v>
       </c>
+      <c r="O89" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I90" s="2">
@@ -5417,6 +5438,9 @@
       </c>
       <c r="N90" t="s">
         <v>121</v>
+      </c>
+      <c r="O90" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.6">
@@ -5439,6 +5463,9 @@
       <c r="N91" t="s">
         <v>122</v>
       </c>
+      <c r="O91" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I92" s="2">
@@ -5460,6 +5487,9 @@
       <c r="N92" t="s">
         <v>72</v>
       </c>
+      <c r="O92" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I93" s="2">
@@ -5481,6 +5511,9 @@
       <c r="N93" t="s">
         <v>68</v>
       </c>
+      <c r="O93" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I94" s="2">
@@ -5502,6 +5535,9 @@
       <c r="N94" t="s">
         <v>122</v>
       </c>
+      <c r="O94" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A95" t="s">
@@ -5697,8 +5733,8 @@
       <c r="I103" s="2">
         <v>9</v>
       </c>
-      <c r="J103">
-        <v>9</v>
+      <c r="J103" t="s">
+        <v>569</v>
       </c>
       <c r="K103" t="s">
         <v>39</v>
@@ -6144,8 +6180,8 @@
       <c r="I122" s="2">
         <v>10</v>
       </c>
-      <c r="J122" t="s">
-        <v>567</v>
+      <c r="J122">
+        <v>10</v>
       </c>
       <c r="K122" t="s">
         <v>108</v>
@@ -11650,8 +11686,8 @@
       <c r="I347" s="2">
         <v>9</v>
       </c>
-      <c r="J347">
-        <v>9</v>
+      <c r="J347" t="s">
+        <v>569</v>
       </c>
       <c r="K347" t="s">
         <v>57</v>
@@ -15495,8 +15531,8 @@
       <c r="I504" s="2">
         <v>9</v>
       </c>
-      <c r="J504">
-        <v>9</v>
+      <c r="J504" t="s">
+        <v>569</v>
       </c>
       <c r="K504" t="s">
         <v>287</v>
@@ -15751,8 +15787,8 @@
       <c r="I515" s="2">
         <v>9</v>
       </c>
-      <c r="J515">
-        <v>9</v>
+      <c r="J515" t="s">
+        <v>569</v>
       </c>
       <c r="K515" t="s">
         <v>57</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCF6ADA-CC43-4C08-ABED-EB04B1149E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04EA358-4B93-4D3E-90F9-5EE989D8B736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -18643,6 +18643,9 @@
       <c r="I629" s="2">
         <v>2</v>
       </c>
+      <c r="J629">
+        <v>2</v>
+      </c>
       <c r="K629" t="s">
         <v>178</v>
       </c>
@@ -18661,6 +18664,9 @@
       <c r="I630" s="2">
         <v>3</v>
       </c>
+      <c r="J630">
+        <v>3</v>
+      </c>
       <c r="K630" t="s">
         <v>210</v>
       </c>
@@ -18677,6 +18683,9 @@
     </row>
     <row r="631" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I631" s="2">
+        <v>4</v>
+      </c>
+      <c r="J631">
         <v>4</v>
       </c>
       <c r="K631" t="s">
@@ -19354,6 +19363,9 @@
       <c r="I658" s="2">
         <v>2</v>
       </c>
+      <c r="J658">
+        <v>2</v>
+      </c>
       <c r="K658" t="s">
         <v>284</v>
       </c>
@@ -19372,6 +19384,9 @@
       <c r="I659" s="2">
         <v>3</v>
       </c>
+      <c r="J659">
+        <v>3</v>
+      </c>
       <c r="K659" t="s">
         <v>177</v>
       </c>
@@ -19388,6 +19403,9 @@
     </row>
     <row r="660" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I660" s="2">
+        <v>4</v>
+      </c>
+      <c r="J660">
         <v>4</v>
       </c>
       <c r="K660" t="s">
@@ -19408,6 +19426,9 @@
       <c r="I661" s="2">
         <v>5</v>
       </c>
+      <c r="J661">
+        <v>5</v>
+      </c>
       <c r="K661" t="s">
         <v>178</v>
       </c>
@@ -19447,6 +19468,9 @@
       <c r="I663" s="2">
         <v>7</v>
       </c>
+      <c r="J663">
+        <v>2</v>
+      </c>
       <c r="K663" t="s">
         <v>287</v>
       </c>
@@ -19465,6 +19489,9 @@
       <c r="I664" s="2">
         <v>8</v>
       </c>
+      <c r="J664">
+        <v>3</v>
+      </c>
       <c r="K664" t="s">
         <v>210</v>
       </c>
@@ -19483,6 +19510,9 @@
       <c r="I665" s="2">
         <v>9</v>
       </c>
+      <c r="J665">
+        <v>4</v>
+      </c>
       <c r="K665" t="s">
         <v>177</v>
       </c>
@@ -19571,6 +19601,9 @@
       <c r="I668" s="2">
         <v>2</v>
       </c>
+      <c r="J668">
+        <v>2</v>
+      </c>
       <c r="K668" t="s">
         <v>287</v>
       </c>
@@ -19589,6 +19622,9 @@
       <c r="I669" s="2">
         <v>3</v>
       </c>
+      <c r="J669">
+        <v>3</v>
+      </c>
       <c r="K669" t="s">
         <v>284</v>
       </c>
@@ -19605,6 +19641,9 @@
     </row>
     <row r="670" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I670" s="2">
+        <v>4</v>
+      </c>
+      <c r="J670">
         <v>4</v>
       </c>
       <c r="K670" t="s">
@@ -19625,6 +19664,9 @@
       <c r="I671" s="2">
         <v>5</v>
       </c>
+      <c r="J671">
+        <v>5</v>
+      </c>
       <c r="K671" t="s">
         <v>178</v>
       </c>
@@ -19664,6 +19706,9 @@
       <c r="I673" s="2">
         <v>7</v>
       </c>
+      <c r="J673">
+        <v>2</v>
+      </c>
       <c r="K673" t="s">
         <v>133</v>
       </c>
@@ -19682,6 +19727,9 @@
       <c r="I674" s="2">
         <v>8</v>
       </c>
+      <c r="J674">
+        <v>3</v>
+      </c>
       <c r="K674" t="s">
         <v>177</v>
       </c>
@@ -19700,6 +19748,9 @@
       <c r="I675" s="2">
         <v>9</v>
       </c>
+      <c r="J675">
+        <v>4</v>
+      </c>
       <c r="K675" t="s">
         <v>178</v>
       </c>
@@ -19717,6 +19768,9 @@
     <row r="676" spans="1:14" x14ac:dyDescent="0.6">
       <c r="I676" s="2">
         <v>10</v>
+      </c>
+      <c r="J676">
+        <v>5</v>
       </c>
       <c r="K676" t="s">
         <v>284</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04EA358-4B93-4D3E-90F9-5EE989D8B736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3442C6-99BB-4CB2-9DD3-C05DE3F08843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -8169,16 +8169,16 @@
         <v>승</v>
       </c>
       <c r="E203">
-        <f>COUNTIF(M203:M210,"승")</f>
+        <f>COUNTIF(M203:M207,"승")</f>
         <v>5</v>
       </c>
       <c r="F203">
-        <f>COUNTA(M203:M210)-E203</f>
-        <v>3</v>
+        <f>COUNTA(M203:M207)-E203</f>
+        <v>0</v>
       </c>
       <c r="G203" s="1">
         <f>E203/(E203+F203)</f>
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="I203" s="2">
         <v>1</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7032DFD-7808-4270-A7CB-5557F051AB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4525DE9-6D75-4C35-B003-54C90FA849E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4357" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1134">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3927,6 +3927,54 @@
   </si>
   <si>
     <t>https://youtu.be/_f07xXh31IE?si=GzY58RpcS6D70L4m&amp;t=10663</t>
+  </si>
+  <si>
+    <t>2026.06.01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타워즈 4강</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>찌킹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진땅콩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임조이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지두두</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아리송이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>백원이야</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄보리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소심</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쟈닌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -30029,11 +30077,11 @@
       </c>
       <c r="F964">
         <f>COUNTA(M964:M972)-E964</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G964" s="1">
         <f>E964/(E964+F964)</f>
-        <v>0.42857142857142855</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I964" s="2">
         <v>1</v>
@@ -30069,7 +30117,7 @@
         <v>798</v>
       </c>
       <c r="L965" t="str">
-        <f t="shared" ref="L965:L970" si="18">IFERROR(INDEX($R$2:$R$99,MATCH(K965,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L965:L971" si="18">IFERROR(INDEX($R$2:$R$99,MATCH(K965,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
       <c r="M965" t="s">
@@ -30203,129 +30251,226 @@
       </c>
     </row>
     <row r="971" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="J971" s="2"/>
+      <c r="A971" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B971" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C971" t="s">
+        <v>55</v>
+      </c>
+      <c r="D971" t="str">
+        <f>IF(E971&gt;F971,"승",IF(E971&lt;F971,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E971">
+        <f>COUNTIF(M971:M979,"승")</f>
+        <v>0</v>
+      </c>
+      <c r="F971">
+        <f>COUNTA(M971:M979)-E971</f>
+        <v>5</v>
+      </c>
+      <c r="G971" s="1">
+        <f>E971/(E971+F971)</f>
+        <v>0</v>
+      </c>
+      <c r="H971" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I971" s="2">
+        <v>1</v>
+      </c>
+      <c r="J971" s="2">
+        <v>1</v>
+      </c>
+      <c r="K971" t="s">
+        <v>1125</v>
+      </c>
+      <c r="L971" t="str">
+        <f t="shared" si="18"/>
+        <v>Z</v>
+      </c>
+      <c r="M971" t="s">
+        <v>4</v>
+      </c>
+      <c r="N971" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="972" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I972" s="2">
+        <v>2</v>
+      </c>
+      <c r="J972" s="2">
+        <v>2</v>
+      </c>
+      <c r="K972" t="s">
+        <v>1126</v>
+      </c>
       <c r="L972" t="str">
         <f t="shared" si="15"/>
-        <v/>
+        <v>P</v>
+      </c>
+      <c r="M972" t="s">
+        <v>4</v>
+      </c>
+      <c r="N972" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="973" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I973" s="2">
+        <v>3</v>
+      </c>
+      <c r="J973" s="2">
+        <v>3</v>
+      </c>
+      <c r="K973" t="s">
+        <v>1127</v>
+      </c>
       <c r="L973" t="str">
         <f t="shared" si="15"/>
-        <v/>
+        <v>Z</v>
+      </c>
+      <c r="M973" t="s">
+        <v>4</v>
+      </c>
+      <c r="N973" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="974" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I974" s="2">
+        <v>4</v>
+      </c>
+      <c r="J974" s="2">
+        <v>4</v>
+      </c>
+      <c r="K974" t="s">
+        <v>1128</v>
+      </c>
       <c r="L974" t="str">
         <f t="shared" si="15"/>
-        <v/>
+        <v>T</v>
+      </c>
+      <c r="M974" t="s">
+        <v>4</v>
+      </c>
+      <c r="N974" t="s">
+        <v>1132</v>
       </c>
     </row>
     <row r="975" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I975" s="2">
+        <v>5</v>
+      </c>
+      <c r="J975" s="2">
+        <v>5</v>
+      </c>
+      <c r="K975" t="s">
+        <v>1129</v>
+      </c>
       <c r="L975" t="str">
         <f t="shared" si="15"/>
-        <v/>
+        <v>P</v>
+      </c>
+      <c r="M975" t="s">
+        <v>4</v>
+      </c>
+      <c r="N975" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="976" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="L976" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="977" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L977" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="978" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L978" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="979" spans="12:12" x14ac:dyDescent="0.6">
+      <c r="J976" s="2"/>
+    </row>
+    <row r="977" spans="10:12" x14ac:dyDescent="0.6">
+      <c r="J977" s="2"/>
+    </row>
+    <row r="978" spans="10:12" x14ac:dyDescent="0.6">
+      <c r="J978" s="2"/>
+    </row>
+    <row r="979" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L979" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="980" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="980" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L980" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="981" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="981" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L981" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="982" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="982" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L982" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="983" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="983" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L983" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="984" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="984" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L984" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="985" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="985" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L985" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="986" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="986" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L986" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="987" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="987" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L987" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="988" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="988" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L988" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="989" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="989" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L989" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="990" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="990" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L990" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="991" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="991" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L991" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="992" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="992" spans="10:12" x14ac:dyDescent="0.6">
       <c r="L992" t="str">
         <f t="shared" si="15"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4525DE9-6D75-4C35-B003-54C90FA849E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2927983B-3E29-47E1-8BA8-8D460F2916FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4468" uniqueCount="1205">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3975,6 +3975,230 @@
   <si>
     <t>쟈닌</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/NeqyY8yGTp4?si=ZufVX4nwJDoNZphg&amp;t=4812</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NeqyY8yGTp4?si=RCZh2dEsEX1rK1CJ&amp;t=5647</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NeqyY8yGTp4?si=B-tWg9vJ2dCoPtW-&amp;t=6813</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NeqyY8yGTp4?si=ui5ssbhV8fx_mY_O&amp;t=7917</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NeqyY8yGTp4?si=lEgxMzD-yRujS0NF&amp;t=9482</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=--UZv7ccwVcoj97-&amp;t=2129</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=vBa5QlFCUAQFlmZ3&amp;t=2588</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=zhc2ZFfNo9giCtT9&amp;t=3860</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=Eiv4jPasEuQCMUZL&amp;t=4622</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=suhOfD1wHAJyyqgM&amp;t=5740</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=1mDmiD1shi6NbpxF&amp;t=5741</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=805kys2vqeZtP7Zd&amp;t=8476</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=r_tjh3F_nA3S52ih&amp;t=10902</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=6WVHomE7_7XtFyvC&amp;t=12329</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7X4-Ig1gs4E?si=YuWVSkLSDy2YBQ5-&amp;t=14529</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=ecOwIkSihCPHcXaY&amp;t=2443</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=sHiB-oDWWKhRMWO3&amp;t=2963</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=5Ow2vxSLmJUnAn5v&amp;t=4157</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=-uizRXW9PhwhHF9g&amp;t=4926</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=bzyAkjmiz2p2qYfn&amp;t=5912</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=2P3PB09ha9od5f1Y&amp;t=6612</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=Q6-bIhtw020eT3nD&amp;t=7393</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=_pE_qzLO0I9CF6vX&amp;t=8152</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=uwg5YIr7eh_2fDgy&amp;t=9979</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=tJ43QrOpT4lhbYlY&amp;t=11322</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ie8DSI7BMVE?si=dVC6TlNoqFt4vdwC&amp;t=12366</t>
+  </si>
+  <si>
+    <t>2025.03.04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=StfwH_t_uDG-oXDw&amp;t=3624</t>
+  </si>
+  <si>
+    <t>다예</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앵지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>성예량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임조이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한쪼니</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵미유</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>핑핑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=NOAYaGot1h0aPbup&amp;t=4342</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=WFcgKhnZHOFtSbGh&amp;t=5175</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=PUcu_olJi42bJ0pO&amp;t=5551</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=M9jOL2gwaJdC5AsS&amp;t=7100</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=jUBEzceX_yayt_TO&amp;t=8663</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=L_EdlxGf8MQmMNUL&amp;t=10489</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V5G9G0YyI2k?si=fLdQES43z0usH64K&amp;t=11649</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=Tj8eCMUh3ge8BoxT&amp;t=4883</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=uTne-MxELC0TwVHQ&amp;t=6069</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=ZN6wLMOuHx0z9XsV&amp;t=6618</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=GrRe4ATRdkaLSrj2&amp;t=7825</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=eyryedNkmK7cFiUM&amp;t=8712</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=JyRH8BO_PHtuvY_-&amp;t=10520</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=VWCNFLrrb-afco7F&amp;t=11702</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=jZHIZcFuJ4lIlL3S&amp;t=12535</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R20xBuEclug?si=_85AZHS6NFkbF80b&amp;t=13522</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=73VNjE2EfZcCY7im&amp;t=658</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=ox7lTk2API5TWUMP&amp;t=1749</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=tRlIcLsDOuyu3Qh2&amp;t=2813</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=71BDeQiWQLnwmxYE&amp;t=4222</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=Y89DzkydXpberZI1&amp;t=5638</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=Fj62W7Kp8F4K7QEt&amp;t=7552</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=PgYp8aOjkhLW1x6S&amp;t=8613</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=AP3naH0YeESWHMr_&amp;t=10029</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0gDlQUflycU?si=dnKSKELkBkoQobwx&amp;t=11114</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=knsLjyfZGiQUcSFq&amp;t=5637</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=yQEq7fTl9ZKH6IoD&amp;t=6827</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=qbCuQ5wb9cvEl9fQ&amp;t=8155</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=g3omjjNeKT3H_5hD&amp;t=9132</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=KXLyIWVbSeR0dhx8&amp;t=11155</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=ngO6uQLQoC_dKNU6&amp;t=12190</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=YG0o7ssR1Yn0vY_9&amp;t=12786</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=JJQB7Ou-MWdmdeR7&amp;t=13978</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LbCHQVNTPl4?si=U_clcWPX11j0cXyt&amp;t=15113</t>
   </si>
 </sst>
 </file>
@@ -6529,6 +6753,9 @@
         <f>E66/(E66+F66)</f>
         <v>0.25</v>
       </c>
+      <c r="H66" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="I66" s="2">
         <v>1</v>
       </c>
@@ -22545,6 +22772,9 @@
       <c r="N658" t="s">
         <v>310</v>
       </c>
+      <c r="O658" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="659" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I659" s="2">
@@ -22566,6 +22796,9 @@
       <c r="N659" t="s">
         <v>199</v>
       </c>
+      <c r="O659" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="660" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I660" s="2">
@@ -22587,6 +22820,9 @@
       <c r="N660" t="s">
         <v>73</v>
       </c>
+      <c r="O660" t="s">
+        <v>1141</v>
+      </c>
     </row>
     <row r="661" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I661" s="2">
@@ -22607,6 +22843,9 @@
       </c>
       <c r="N661" t="s">
         <v>102</v>
+      </c>
+      <c r="O661" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="662" spans="1:15" x14ac:dyDescent="0.6">
@@ -22629,6 +22868,9 @@
       <c r="N662" t="s">
         <v>68</v>
       </c>
+      <c r="O662" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="663" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I663" s="2">
@@ -22650,6 +22892,9 @@
       <c r="N663" t="s">
         <v>68</v>
       </c>
+      <c r="O663" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="664" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I664" s="2">
@@ -22671,6 +22916,9 @@
       <c r="N664" t="s">
         <v>310</v>
       </c>
+      <c r="O664" t="s">
+        <v>1145</v>
+      </c>
     </row>
     <row r="665" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I665" s="2">
@@ -22692,6 +22940,9 @@
       <c r="N665" t="s">
         <v>102</v>
       </c>
+      <c r="O665" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="666" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I666" s="2">
@@ -22713,6 +22964,9 @@
       <c r="N666" t="s">
         <v>73</v>
       </c>
+      <c r="O666" t="s">
+        <v>1147</v>
+      </c>
     </row>
     <row r="667" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I667" s="2">
@@ -22734,6 +22988,9 @@
       <c r="N667" t="s">
         <v>310</v>
       </c>
+      <c r="O667" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="668" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A668" t="s">
@@ -22783,6 +23040,9 @@
       <c r="N668" t="s">
         <v>332</v>
       </c>
+      <c r="O668" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="669" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I669" s="2">
@@ -22804,6 +23064,9 @@
       <c r="N669" t="s">
         <v>287</v>
       </c>
+      <c r="O669" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="670" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I670" s="2">
@@ -22825,6 +23088,9 @@
       <c r="N670" t="s">
         <v>333</v>
       </c>
+      <c r="O670" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="671" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I671" s="2">
@@ -22845,6 +23111,9 @@
       </c>
       <c r="N671" t="s">
         <v>293</v>
+      </c>
+      <c r="O671" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="672" spans="1:15" x14ac:dyDescent="0.6">
@@ -22867,8 +23136,11 @@
       <c r="N672" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="673" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O672" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="673" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I673" s="2">
         <v>6</v>
       </c>
@@ -22888,8 +23160,11 @@
       <c r="N673" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="674" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O673" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="674" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I674" s="2">
         <v>7</v>
       </c>
@@ -22909,8 +23184,11 @@
       <c r="N674" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="675" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O674" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="675" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I675" s="2">
         <v>8</v>
       </c>
@@ -22930,8 +23208,11 @@
       <c r="N675" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="676" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O675" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="676" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I676" s="2">
         <v>9</v>
       </c>
@@ -22951,8 +23232,11 @@
       <c r="N676" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="677" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O676" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="677" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I677" s="2">
         <v>10</v>
       </c>
@@ -22972,8 +23256,11 @@
       <c r="N677" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="678" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O677" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="678" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I678" s="2">
         <v>11</v>
       </c>
@@ -22993,8 +23280,11 @@
       <c r="N678" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="679" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O678" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="679" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A679" t="s">
         <v>335</v>
       </c>
@@ -23042,8 +23332,11 @@
       <c r="N679" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="680" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O679" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="680" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I680" s="2">
         <v>2</v>
       </c>
@@ -23063,8 +23356,11 @@
       <c r="N680" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="681" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O680" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="681" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I681" s="2">
         <v>3</v>
       </c>
@@ -23084,8 +23380,11 @@
       <c r="N681" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="682" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O681" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="682" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I682" s="2">
         <v>4</v>
       </c>
@@ -23105,8 +23404,11 @@
       <c r="N682" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="683" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O682" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="683" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I683" s="2">
         <v>5</v>
       </c>
@@ -23126,8 +23428,11 @@
       <c r="N683" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="684" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O683" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="684" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I684" s="2">
         <v>6</v>
       </c>
@@ -23147,8 +23452,11 @@
       <c r="N684" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="685" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O684" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="685" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I685" s="2">
         <v>7</v>
       </c>
@@ -23168,8 +23476,11 @@
       <c r="N685" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="686" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O685" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="686" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I686" s="2">
         <v>8</v>
       </c>
@@ -23189,8 +23500,11 @@
       <c r="N686" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="687" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O686" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="687" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I687" s="2">
         <v>9</v>
       </c>
@@ -23210,8 +23524,11 @@
       <c r="N687" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="688" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O687" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="688" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A688" t="s">
         <v>336</v>
       </c>
@@ -23259,8 +23576,11 @@
       <c r="N688" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="689" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O688" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="689" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I689" s="2">
         <v>2</v>
       </c>
@@ -23280,8 +23600,11 @@
       <c r="N689" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="690" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O689" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="690" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I690" s="2">
         <v>3</v>
       </c>
@@ -23301,8 +23624,11 @@
       <c r="N690" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="691" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O690" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="691" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I691" s="2">
         <v>4</v>
       </c>
@@ -23322,8 +23648,11 @@
       <c r="N691" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="692" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O691" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="692" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I692" s="2">
         <v>5</v>
       </c>
@@ -23343,8 +23672,11 @@
       <c r="N692" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="693" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O692" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="693" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I693" s="2">
         <v>6</v>
       </c>
@@ -23364,8 +23696,11 @@
       <c r="N693" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="694" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O693" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="694" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I694" s="2">
         <v>7</v>
       </c>
@@ -23385,8 +23720,11 @@
       <c r="N694" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="695" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O694" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="695" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I695" s="2">
         <v>8</v>
       </c>
@@ -23406,8 +23744,11 @@
       <c r="N695" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="696" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O695" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="696" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I696" s="2">
         <v>9</v>
       </c>
@@ -23427,8 +23768,11 @@
       <c r="N696" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="697" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O696" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="697" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A697" t="s">
         <v>337</v>
       </c>
@@ -23475,8 +23819,11 @@
       <c r="N697" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="698" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O697" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="698" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I698" s="2">
         <v>2</v>
       </c>
@@ -23496,8 +23843,11 @@
       <c r="N698" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="699" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O698" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="699" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I699" s="2">
         <v>3</v>
       </c>
@@ -23517,8 +23867,11 @@
       <c r="N699" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="700" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O699" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I700" s="2">
         <v>4</v>
       </c>
@@ -23538,8 +23891,11 @@
       <c r="N700" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="701" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O700" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="701" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I701" s="2">
         <v>5</v>
       </c>
@@ -23559,8 +23915,11 @@
       <c r="N701" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="702" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O701" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="702" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I702" s="2">
         <v>6</v>
       </c>
@@ -23580,8 +23939,11 @@
       <c r="N702" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="703" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O702" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="703" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I703" s="2">
         <v>7</v>
       </c>
@@ -23601,8 +23963,11 @@
       <c r="N703" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="704" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O703" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="704" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I704" s="2">
         <v>8</v>
       </c>
@@ -23622,8 +23987,11 @@
       <c r="N704" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="705" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O704" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="705" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I705" s="2">
         <v>9</v>
       </c>
@@ -23643,8 +24011,11 @@
       <c r="N705" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="706" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O705" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="706" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A706" t="s">
         <v>339</v>
       </c>
@@ -23693,7 +24064,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="707" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="707" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I707" s="2">
         <v>2</v>
       </c>
@@ -23714,7 +24085,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="708" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I708" s="2">
         <v>3</v>
       </c>
@@ -23735,7 +24106,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="709" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I709" s="2">
         <v>4</v>
       </c>
@@ -23756,7 +24127,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="710" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I710" s="2">
         <v>5</v>
       </c>
@@ -23777,7 +24148,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="711" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="711" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I711" s="2">
         <v>6</v>
       </c>
@@ -23798,7 +24169,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="712" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="712" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A712" t="s">
         <v>340</v>
       </c>
@@ -23845,7 +24216,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="713" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="713" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I713" s="2">
         <v>2</v>
       </c>
@@ -23866,7 +24237,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="714" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="714" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I714" s="2">
         <v>3</v>
       </c>
@@ -23887,7 +24258,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="715" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="715" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I715" s="2">
         <v>4</v>
       </c>
@@ -23908,7 +24279,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="716" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="716" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I716" s="2">
         <v>5</v>
       </c>
@@ -23929,7 +24300,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="717" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="717" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I717" s="2">
         <v>6</v>
       </c>
@@ -23950,7 +24321,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="718" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="718" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I718" s="2">
         <v>7</v>
       </c>
@@ -23971,7 +24342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="719" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="719" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A719" t="s">
         <v>342</v>
       </c>
@@ -24020,7 +24391,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="720" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="720" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I720" s="2">
         <v>2</v>
       </c>
@@ -30265,11 +30636,11 @@
         <v>패</v>
       </c>
       <c r="E971">
-        <f>COUNTIF(M971:M979,"승")</f>
+        <f>COUNTIF(M971:M975,"승")</f>
         <v>0</v>
       </c>
       <c r="F971">
-        <f>COUNTA(M971:M979)-E971</f>
+        <f>COUNTA(M971:M975)-E971</f>
         <v>5</v>
       </c>
       <c r="G971" s="1">
@@ -30298,6 +30669,9 @@
       <c r="N971" t="s">
         <v>102</v>
       </c>
+      <c r="O971" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="972" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I972" s="2">
@@ -30319,6 +30693,9 @@
       <c r="N972" t="s">
         <v>1130</v>
       </c>
+      <c r="O972" t="s">
+        <v>1135</v>
+      </c>
     </row>
     <row r="973" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I973" s="2">
@@ -30339,6 +30716,9 @@
       </c>
       <c r="N973" t="s">
         <v>1131</v>
+      </c>
+      <c r="O973" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="974" spans="1:15" x14ac:dyDescent="0.6">
@@ -30361,6 +30741,9 @@
       <c r="N974" t="s">
         <v>1132</v>
       </c>
+      <c r="O974" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="975" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I975" s="2">
@@ -30382,95 +30765,279 @@
       <c r="N975" t="s">
         <v>1133</v>
       </c>
+      <c r="O975" t="s">
+        <v>1138</v>
+      </c>
     </row>
     <row r="976" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="J976" s="2"/>
-    </row>
-    <row r="977" spans="10:12" x14ac:dyDescent="0.6">
-      <c r="J977" s="2"/>
-    </row>
-    <row r="978" spans="10:12" x14ac:dyDescent="0.6">
-      <c r="J978" s="2"/>
-    </row>
-    <row r="979" spans="10:12" x14ac:dyDescent="0.6">
+      <c r="A976" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B976" t="s">
+        <v>110</v>
+      </c>
+      <c r="C976" t="s">
+        <v>94</v>
+      </c>
+      <c r="D976" t="str">
+        <f>IF(E976&gt;F976,"승",IF(E976&lt;F976,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E976">
+        <f>COUNTIF(M976:M980,"승")</f>
+        <v>1</v>
+      </c>
+      <c r="F976">
+        <f>COUNTA(M976:M980)-E976</f>
+        <v>4</v>
+      </c>
+      <c r="G976" s="1">
+        <f>E976/(E976+F976)</f>
+        <v>0.2</v>
+      </c>
+      <c r="H976" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I976" s="2">
+        <v>1</v>
+      </c>
+      <c r="J976" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K976" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L976" t="str">
+        <f t="shared" si="15"/>
+        <v>Z</v>
+      </c>
+      <c r="M976" t="s">
+        <v>3</v>
+      </c>
+      <c r="N976" t="s">
+        <v>1163</v>
+      </c>
+      <c r="O976" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="977" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I977" s="2">
+        <v>2</v>
+      </c>
+      <c r="J977" s="2">
+        <v>2</v>
+      </c>
+      <c r="K977" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L977" t="str">
+        <f t="shared" si="15"/>
+        <v>Z</v>
+      </c>
+      <c r="M977" t="s">
+        <v>4</v>
+      </c>
+      <c r="N977" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O977" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="978" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I978" s="2">
+        <v>3</v>
+      </c>
+      <c r="J978" s="2">
+        <v>3</v>
+      </c>
+      <c r="K978" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L978" t="str">
+        <f t="shared" si="15"/>
+        <v>Z</v>
+      </c>
+      <c r="M978" t="s">
+        <v>4</v>
+      </c>
+      <c r="N978" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O978" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="979" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I979" s="2">
+        <v>4</v>
+      </c>
+      <c r="J979" s="2">
+        <v>4</v>
+      </c>
+      <c r="K979" t="s">
+        <v>1167</v>
+      </c>
       <c r="L979" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="980" spans="10:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M979" t="s">
+        <v>4</v>
+      </c>
+      <c r="N979" t="s">
+        <v>1169</v>
+      </c>
+      <c r="O979" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="980" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I980" s="2">
+        <v>5</v>
+      </c>
+      <c r="J980" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K980" t="s">
+        <v>1166</v>
+      </c>
       <c r="L980" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="981" spans="10:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M980" t="s">
+        <v>4</v>
+      </c>
+      <c r="N980" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O980" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="981" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I981" s="2">
+        <v>6</v>
+      </c>
+      <c r="J981" s="2">
+        <v>2</v>
+      </c>
+      <c r="K981" t="s">
+        <v>1162</v>
+      </c>
       <c r="L981" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="982" spans="10:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M981" t="s">
+        <v>3</v>
+      </c>
+      <c r="N981" t="s">
+        <v>1163</v>
+      </c>
+      <c r="O981" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="982" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I982" s="2">
+        <v>7</v>
+      </c>
+      <c r="J982" s="2">
+        <v>3</v>
+      </c>
+      <c r="K982" t="s">
+        <v>1164</v>
+      </c>
       <c r="L982" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="983" spans="10:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M982" t="s">
+        <v>4</v>
+      </c>
+      <c r="N982" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O982" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="983" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I983" s="2">
+        <v>8</v>
+      </c>
+      <c r="J983" s="2">
+        <v>4</v>
+      </c>
+      <c r="K983" t="s">
+        <v>1167</v>
+      </c>
       <c r="L983" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="984" spans="10:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M983" t="s">
+        <v>4</v>
+      </c>
+      <c r="N983" t="s">
+        <v>1169</v>
+      </c>
+      <c r="O983" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="984" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L984" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="985" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="985" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L985" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="986" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="986" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L986" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="987" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="987" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L987" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="988" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="988" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L988" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="989" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="989" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L989" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="990" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="990" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L990" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="991" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="991" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L991" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="992" spans="10:12" x14ac:dyDescent="0.6">
+    <row r="992" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L992" t="str">
         <f t="shared" si="15"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2927983B-3E29-47E1-8BA8-8D460F2916FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ECF69B-9CB9-4D0D-97B0-3EE8252313BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -30250,19 +30250,19 @@
       </c>
       <c r="D957" t="str">
         <f>IF(E957&gt;F957,"승",IF(E957&lt;F957,"패"))</f>
-        <v>패</v>
+        <v>승</v>
       </c>
       <c r="E957">
-        <f>COUNTIF(M957:M965,"승")</f>
+        <f>COUNTIF(M957:M963,"승")</f>
         <v>4</v>
       </c>
       <c r="F957">
-        <f>COUNTA(M957:M965)-E957</f>
-        <v>5</v>
+        <f>COUNTA(M957:M963)-E957</f>
+        <v>3</v>
       </c>
       <c r="G957" s="1">
         <f>E957/(E957+F957)</f>
-        <v>0.44444444444444442</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I957" s="2">
         <v>1</v>
@@ -30443,16 +30443,16 @@
         <v>패</v>
       </c>
       <c r="E964">
-        <f>COUNTIF(M964:M972,"승")</f>
+        <f>COUNTIF(M964:M970,"승")</f>
         <v>3</v>
       </c>
       <c r="F964">
-        <f>COUNTA(M964:M972)-E964</f>
-        <v>6</v>
+        <f>COUNTA(M964:M970)-E964</f>
+        <v>4</v>
       </c>
       <c r="G964" s="1">
         <f>E964/(E964+F964)</f>
-        <v>0.33333333333333331</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I964" s="2">
         <v>1</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ECF69B-9CB9-4D0D-97B0-3EE8252313BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD4D25A-36A3-4F98-BA51-D5139960460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -21,21 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4468" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4573" uniqueCount="1285">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4199,6 +4190,267 @@
   </si>
   <si>
     <t>https://youtu.be/LbCHQVNTPl4?si=U_clcWPX11j0cXyt&amp;t=15113</t>
+  </si>
+  <si>
+    <t>2026.06.02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>갯벌스타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지두두</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>치리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>찌킹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>패</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디임</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요닝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>효짱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>란란</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남수댕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>졈니</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=i18kVBuvDD3CU2pV&amp;t=2251</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=oR8YN-mMTevZKwp6&amp;t=4467</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=qgeIboeelOtzCUAP&amp;t=5823</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=uSXQGcNqsPhPnVZr&amp;t=6911</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=ZyaGZ2zZo1IfSIUj&amp;t=8714</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=DjAv_Wjv3mFOTPSN&amp;t=10992</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ycD_eTwxDN4?si=tZHd3-6x_oDHSLLb&amp;t=13598</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=CLMFp6Pw0glZk6sy&amp;t=971</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=rR1GqtjfeZUUhmPq&amp;t=2601</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=_IMiCf8A5LfEpdAj&amp;t=3246</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=TW4X4dbS_0d8zNkD&amp;t=4992</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=qC8l1AObZQJBYsvz&amp;t=5883</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sfKaz7chfh4?si=FjpGxy3HATNk9wGH&amp;t=6923</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=5Abx_5F_WpApMQg6&amp;t=4698</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=1ZkwTCV43_EN2tGB&amp;t=5993</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=N3aLVdxfx5DZ5Hkh&amp;t=6639</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=mZQ5CHHi_ptxR7kn&amp;t=7472</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=sqgHe6az_Bm1jzSK&amp;t=8530</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=EIAysOmgkRRUKIsn&amp;t=9769</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aZJHouR4Y7k?si=ttEtz78oQZTsE_BY&amp;t=10254</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CvT2Tvgm09o?si=T9tdRyxorz8yXnep&amp;t=2150</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CvT2Tvgm09o?si=56JZh7DX8CBkyMxe&amp;t=5755</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CvT2Tvgm09o?si=cK47gHME310-cPyW&amp;t=8943</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JHT85Q2VrEs?si=i67zmHH5lP9EeLtG&amp;t=146</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JHT85Q2VrEs?si=NHkunz4CxaC3dfCT&amp;t=2367</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JHT85Q2VrEs?si=uuft4wuhHk_q6jjp&amp;t=4059</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JHT85Q2VrEs?si=TiaP8O6JZMBAzqfS&amp;t=5755</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=Ua1ejmERVSHR3cfA&amp;t=3721</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=fQMuaJviW7swniS4&amp;t=5160</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=lAEVeuzISD9RsU73&amp;t=7976</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=LVIpuObQovn-dkxM&amp;t=9675</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=ieGlXet0uL6V9Ffq&amp;t=11211</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=GCA4-iVaxSzhboET&amp;t=13441</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iiftvtuiKLM?si=Qg-Nmg6Av3f3UaeD&amp;t=15159</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=Q4xQdjZWBFufv56x&amp;t=2996</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=vDcMdOyPKjZLFrDJ&amp;t=4398</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=iiHVVldXbTNNqz9e&amp;t=5885</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=yiX3RxgHX7OpEtWW&amp;t=7921</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=FxaxlIsJh-aTFrNA&amp;t=6425</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=8W1cDejJv2f575fQ&amp;t=9179</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=c6dunocl1-Ji3KYg&amp;t=11466</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QDRrM3af3cQ?si=il6ntbylRbckLLM2&amp;t=9808</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=yYBCdzFQ9KOWLRgC&amp;t=3018</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=NmKP-oArGdKlkqtr&amp;t=3720</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=7crjCPIiu1INOdf_&amp;t=5190</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=E1DVd2vFTE_KLYuu&amp;t=5893</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=XDHfFFNU1Ynt0Nos&amp;t=6723</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OC427CN9i4U?si=0bgylxq5FyudJTUh&amp;t=7941</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sveWh1Abl2o?si=S1wQxpZU--NXtN0T&amp;t=2729</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sveWh1Abl2o?si=bLhxaoxTiHD6eZje&amp;t=3431</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sveWh1Abl2o?si=n2ttDnfb3b9E6ZgG&amp;t=4496</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sveWh1Abl2o?si=iBV7fnhvXbbqduTM&amp;t=5874</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sveWh1Abl2o?si=1qfVgJBUEKMmekAa&amp;t=7609</t>
+  </si>
+  <si>
+    <t>2025.11.21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앵지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쥬나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=l6OhWWHa63g4x63f&amp;t=4451</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=OKraQnkSlXhCav8r&amp;t=4847</t>
+  </si>
+  <si>
+    <t>선정은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>세나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>또봉순</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=BDjxHyteiTcK2IjE&amp;t=5271</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=L_QNfWry1OX5-Alk&amp;t=5690</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=YbXwhOq8rpmgyGBZ&amp;t=6094</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VQa5eO2jnqs?si=aRAPPoMDa8AW_mL6&amp;t=7827</t>
   </si>
 </sst>
 </file>
@@ -24063,6 +24315,9 @@
       <c r="N706" t="s">
         <v>225</v>
       </c>
+      <c r="O706" t="s">
+        <v>1227</v>
+      </c>
     </row>
     <row r="707" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I707" s="2">
@@ -24084,6 +24339,9 @@
       <c r="N707" t="s">
         <v>36</v>
       </c>
+      <c r="O707" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="708" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I708" s="2">
@@ -24105,6 +24363,9 @@
       <c r="N708" t="s">
         <v>228</v>
       </c>
+      <c r="O708" t="s">
+        <v>1229</v>
+      </c>
     </row>
     <row r="709" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I709" s="2">
@@ -24125,6 +24386,9 @@
       </c>
       <c r="N709" t="s">
         <v>229</v>
+      </c>
+      <c r="O709" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="710" spans="1:15" x14ac:dyDescent="0.6">
@@ -24147,6 +24411,9 @@
       <c r="N710" t="s">
         <v>306</v>
       </c>
+      <c r="O710" t="s">
+        <v>1231</v>
+      </c>
     </row>
     <row r="711" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I711" s="2">
@@ -24168,6 +24435,9 @@
       <c r="N711" t="s">
         <v>228</v>
       </c>
+      <c r="O711" t="s">
+        <v>1232</v>
+      </c>
     </row>
     <row r="712" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A712" t="s">
@@ -24177,7 +24447,7 @@
         <v>131</v>
       </c>
       <c r="C712" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="D712" t="str">
         <f>IF(E712&gt;F712,"승",IF(E712&lt;F712,"패"))</f>
@@ -24215,6 +24485,9 @@
       <c r="N712" t="s">
         <v>206</v>
       </c>
+      <c r="O712" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="713" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I713" s="2">
@@ -24236,6 +24509,9 @@
       <c r="N713" t="s">
         <v>135</v>
       </c>
+      <c r="O713" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="714" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I714" s="2">
@@ -24257,6 +24533,9 @@
       <c r="N714" t="s">
         <v>154</v>
       </c>
+      <c r="O714" t="s">
+        <v>1235</v>
+      </c>
     </row>
     <row r="715" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I715" s="2">
@@ -24277,6 +24556,9 @@
       </c>
       <c r="N715" t="s">
         <v>222</v>
+      </c>
+      <c r="O715" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="716" spans="1:15" x14ac:dyDescent="0.6">
@@ -24299,6 +24581,9 @@
       <c r="N716" t="s">
         <v>277</v>
       </c>
+      <c r="O716" t="s">
+        <v>1237</v>
+      </c>
     </row>
     <row r="717" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I717" s="2">
@@ -24320,6 +24605,9 @@
       <c r="N717" t="s">
         <v>341</v>
       </c>
+      <c r="O717" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="718" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I718" s="2">
@@ -24341,6 +24629,9 @@
       <c r="N718" t="s">
         <v>20</v>
       </c>
+      <c r="O718" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="719" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A719" t="s">
@@ -24390,6 +24681,9 @@
       <c r="N719" t="s">
         <v>343</v>
       </c>
+      <c r="O719" t="s">
+        <v>1240</v>
+      </c>
     </row>
     <row r="720" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I720" s="2">
@@ -24411,8 +24705,11 @@
       <c r="N720" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O720" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="721" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I721" s="2">
         <v>3</v>
       </c>
@@ -24432,8 +24729,11 @@
       <c r="N721" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="722" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O721" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="722" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I722" s="2">
         <v>4</v>
       </c>
@@ -24453,8 +24753,11 @@
       <c r="N722" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O722" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="723" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I723" s="2">
         <v>5</v>
       </c>
@@ -24474,8 +24777,11 @@
       <c r="N723" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O723" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="724" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I724" s="2">
         <v>6</v>
       </c>
@@ -24495,8 +24801,11 @@
       <c r="N724" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="725" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O724" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="725" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I725" s="2">
         <v>7</v>
       </c>
@@ -24516,8 +24825,11 @@
       <c r="N725" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="726" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O725" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="726" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A726" t="s">
         <v>344</v>
       </c>
@@ -24565,8 +24877,11 @@
       <c r="N726" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O726" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="727" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I727" s="2">
         <v>2</v>
       </c>
@@ -24586,8 +24901,11 @@
       <c r="N727" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O727" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="728" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I728" s="2">
         <v>3</v>
       </c>
@@ -24607,8 +24925,11 @@
       <c r="N728" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O728" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I729" s="2">
         <v>4</v>
       </c>
@@ -24628,8 +24949,11 @@
       <c r="N729" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="730" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O729" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="730" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I730" s="2">
         <v>5</v>
       </c>
@@ -24649,8 +24973,11 @@
       <c r="N730" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O730" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="731" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I731" s="2">
         <v>6</v>
       </c>
@@ -24670,8 +24997,11 @@
       <c r="N731" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O731" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="732" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I732" s="2">
         <v>7</v>
       </c>
@@ -24691,8 +25021,11 @@
       <c r="N732" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="733" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O732" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="733" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A733" t="s">
         <v>346</v>
       </c>
@@ -24740,8 +25073,11 @@
       <c r="N733" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="734" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O733" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="734" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I734" s="2">
         <v>2</v>
       </c>
@@ -24761,8 +25097,11 @@
       <c r="N734" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="735" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O734" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="735" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I735" s="2">
         <v>3</v>
       </c>
@@ -24782,8 +25121,11 @@
       <c r="N735" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O735" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="736" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I736" s="2">
         <v>4</v>
       </c>
@@ -24803,8 +25145,11 @@
       <c r="N736" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O736" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="737" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I737" s="2">
         <v>5</v>
       </c>
@@ -24824,8 +25169,11 @@
       <c r="N737" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O737" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="738" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I738" s="2">
         <v>6</v>
       </c>
@@ -24845,8 +25193,11 @@
       <c r="N738" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O738" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="739" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I739" s="2">
         <v>7</v>
       </c>
@@ -24866,8 +25217,11 @@
       <c r="N739" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O739" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="740" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I740" s="2">
         <v>8</v>
       </c>
@@ -24887,8 +25241,11 @@
       <c r="N740" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O740" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="741" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A741" t="s">
         <v>352</v>
       </c>
@@ -24936,8 +25293,11 @@
       <c r="N741" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="742" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O741" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="742" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I742" s="2">
         <v>2</v>
       </c>
@@ -24957,8 +25317,11 @@
       <c r="N742" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="743" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O742" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="743" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I743" s="2">
         <v>3</v>
       </c>
@@ -24978,8 +25341,11 @@
       <c r="N743" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O743" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="744" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I744" s="2">
         <v>4</v>
       </c>
@@ -24999,8 +25365,11 @@
       <c r="N744" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="745" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O744" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="745" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I745" s="2">
         <v>5</v>
       </c>
@@ -25020,8 +25389,11 @@
       <c r="N745" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O745" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="746" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I746" s="2">
         <v>6</v>
       </c>
@@ -25041,8 +25413,11 @@
       <c r="N746" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O746" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A747" t="s">
         <v>356</v>
       </c>
@@ -25090,8 +25465,11 @@
       <c r="N747" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="748" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O747" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="748" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I748" s="2">
         <v>2</v>
       </c>
@@ -25111,8 +25489,11 @@
       <c r="N748" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O748" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="749" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I749" s="2">
         <v>3</v>
       </c>
@@ -25132,8 +25513,11 @@
       <c r="N749" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O749" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="750" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I750" s="2">
         <v>4</v>
       </c>
@@ -25153,8 +25537,11 @@
       <c r="N750" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O750" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="751" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I751" s="2">
         <v>5</v>
       </c>
@@ -25174,8 +25561,11 @@
       <c r="N751" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O751" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="752" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A752" t="s">
         <v>357</v>
       </c>
@@ -30784,16 +31174,16 @@
         <v>패</v>
       </c>
       <c r="E976">
-        <f>COUNTIF(M976:M980,"승")</f>
-        <v>1</v>
+        <f>COUNTIF(M976:M983,"승")</f>
+        <v>2</v>
       </c>
       <c r="F976">
-        <f>COUNTA(M976:M980)-E976</f>
-        <v>4</v>
+        <f>COUNTA(M976:M983)-E976</f>
+        <v>6</v>
       </c>
       <c r="G976" s="1">
         <f>E976/(E976+F976)</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H976" s="1" t="s">
         <v>144</v>
@@ -30821,7 +31211,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="977" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="977" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I977" s="2">
         <v>2</v>
       </c>
@@ -30845,7 +31235,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="978" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="978" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I978" s="2">
         <v>3</v>
       </c>
@@ -30869,7 +31259,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="979" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="979" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I979" s="2">
         <v>4</v>
       </c>
@@ -30893,7 +31283,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="980" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="980" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I980" s="2">
         <v>5</v>
       </c>
@@ -30917,7 +31307,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="981" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="981" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I981" s="2">
         <v>6</v>
       </c>
@@ -30941,7 +31331,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="982" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="982" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I982" s="2">
         <v>7</v>
       </c>
@@ -30965,7 +31355,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="983" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="983" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I983" s="2">
         <v>8</v>
       </c>
@@ -30989,151 +31379,440 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="984" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="984" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A984" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B984" t="s">
+        <v>131</v>
+      </c>
+      <c r="C984" t="s">
+        <v>55</v>
+      </c>
+      <c r="D984" t="str">
+        <f>IF(E984&gt;F984,"승",IF(E984&lt;F984,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E984">
+        <f>COUNTIF(M984:M990,"승")</f>
+        <v>3</v>
+      </c>
+      <c r="F984">
+        <f>COUNTA(M984:M990)-E984</f>
+        <v>4</v>
+      </c>
+      <c r="G984" s="1">
+        <f>E984/(E984+F984)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H984" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I984" s="2">
+        <v>1</v>
+      </c>
+      <c r="J984" s="2">
+        <v>1</v>
+      </c>
+      <c r="K984" t="s">
+        <v>1207</v>
+      </c>
       <c r="L984" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="985" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M984" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N984" t="s">
+        <v>1213</v>
+      </c>
+      <c r="O984" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="985" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I985" s="2">
+        <v>2</v>
+      </c>
+      <c r="J985" s="2">
+        <v>2</v>
+      </c>
+      <c r="K985" t="s">
+        <v>1208</v>
+      </c>
       <c r="L985" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="986" spans="9:15" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M985" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N985" t="s">
+        <v>1214</v>
+      </c>
+      <c r="O985" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="986" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I986" s="2">
+        <v>3</v>
+      </c>
+      <c r="J986" s="2">
+        <v>3</v>
+      </c>
+      <c r="K986" t="s">
+        <v>17</v>
+      </c>
       <c r="L986" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="987" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M986" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N986" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O986" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="987" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I987" s="2">
+        <v>4</v>
+      </c>
+      <c r="J987" s="2">
+        <v>4</v>
+      </c>
+      <c r="K987" t="s">
+        <v>16</v>
+      </c>
       <c r="L987" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="988" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M987" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N987" t="s">
+        <v>1216</v>
+      </c>
+      <c r="O987" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="988" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I988" s="2">
+        <v>5</v>
+      </c>
+      <c r="J988" s="2">
+        <v>5</v>
+      </c>
+      <c r="K988" t="s">
+        <v>18</v>
+      </c>
       <c r="L988" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="989" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M988" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N988" t="s">
+        <v>1217</v>
+      </c>
+      <c r="O988" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="989" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I989" s="2">
+        <v>6</v>
+      </c>
+      <c r="J989" s="2">
+        <v>6</v>
+      </c>
+      <c r="K989" t="s">
+        <v>1209</v>
+      </c>
       <c r="L989" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="990" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M989" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N989" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O989" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="990" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I990" s="2">
+        <v>7</v>
+      </c>
+      <c r="J990" s="2">
+        <v>7</v>
+      </c>
+      <c r="K990" t="s">
+        <v>1210</v>
+      </c>
       <c r="L990" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="991" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M990" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N990" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O990" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="991" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A991" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B991" t="s">
+        <v>347</v>
+      </c>
+      <c r="C991" t="s">
+        <v>94</v>
+      </c>
+      <c r="D991" t="str">
+        <f>IF(E991&gt;F991,"승",IF(E991&lt;F991,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E991">
+        <f>COUNTIF(M991:M996,"승")</f>
+        <v>4</v>
+      </c>
+      <c r="F991">
+        <f>COUNTA(M991:M996)-E991</f>
+        <v>2</v>
+      </c>
+      <c r="G991" s="1">
+        <f>E991/(E991+F991)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H991" s="1"/>
+      <c r="I991" s="2">
+        <v>1</v>
+      </c>
+      <c r="J991" s="2">
+        <v>1</v>
+      </c>
+      <c r="K991" t="s">
+        <v>1274</v>
+      </c>
       <c r="L991" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="992" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M991" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N991" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O991" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="992" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I992" s="2">
+        <v>2</v>
+      </c>
+      <c r="J992" s="2">
+        <v>2</v>
+      </c>
+      <c r="K992" t="s">
+        <v>1209</v>
+      </c>
       <c r="L992" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="993" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M992" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N992" t="s">
+        <v>1278</v>
+      </c>
+      <c r="O992" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="993" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I993" s="2">
+        <v>3</v>
+      </c>
+      <c r="J993" s="2">
+        <v>3</v>
+      </c>
+      <c r="K993" t="s">
+        <v>1279</v>
+      </c>
       <c r="L993" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="994" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M993" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N993" t="s">
+        <v>1280</v>
+      </c>
+      <c r="O993" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="994" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I994" s="2">
+        <v>4</v>
+      </c>
+      <c r="J994" s="2">
+        <v>4</v>
+      </c>
+      <c r="K994" t="s">
+        <v>1279</v>
+      </c>
       <c r="L994" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="995" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M994" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N994" t="s">
+        <v>1280</v>
+      </c>
+      <c r="O994" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="995" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I995" s="2">
+        <v>5</v>
+      </c>
+      <c r="J995" s="2">
+        <v>5</v>
+      </c>
+      <c r="K995" t="s">
+        <v>1209</v>
+      </c>
       <c r="L995" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="996" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M995" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N995" t="s">
+        <v>1278</v>
+      </c>
+      <c r="O995" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="996" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I996" s="2">
+        <v>6</v>
+      </c>
+      <c r="J996" s="2">
+        <v>6</v>
+      </c>
+      <c r="K996" t="s">
+        <v>1274</v>
+      </c>
       <c r="L996" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="997" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M996" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N996" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O996" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="997" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="J997" s="2"/>
       <c r="L997" t="str">
         <f t="shared" ref="L997:L1060" si="19">IFERROR(INDEX($R$2:$R$99,MATCH(K997,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="998" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="998" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L998" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="999" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="999" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L999" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1000" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1000" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1000" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1001" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1001" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1001" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1002" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1002" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1002" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1003" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1003" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1003" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1004" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1004" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1004" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1005" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1005" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1005" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1006" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1006" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1006" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1007" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1007" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1007" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1008" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1008" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1008" t="str">
         <f t="shared" si="19"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69A817F-F961-4B0C-8812-219BB01B5F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C152E897-A1C7-44EE-8C32-74B95D12728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4689" uniqueCount="1375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4698" uniqueCount="1384">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4737,6 +4737,33 @@
   </si>
   <si>
     <t>https://youtu.be/p0gUxmnSZwQ?si=m04fKVwKyj99i0rq&amp;t=8698</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=F9x_uM26ibaGTOYQ&amp;t=475</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=ne0iHpgR2ik4SMYG&amp;t=2161</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=FGa5uflpEp59EFAu&amp;t=3064</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=gSEi29r7PNW2GRdb&amp;t=3469</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=j0GMO_J94aljA4LT&amp;t=4166</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=t7eHBgl54g-spmJU&amp;t=5094</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=BlMPSzyv3yCHGI3r&amp;t=5483</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=zy-Te4XjUzwkVJX4&amp;t=6689</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PX6Vxch1I8?si=89Xcnkv_hbNpFGas&amp;t=8398</t>
   </si>
 </sst>
 </file>
@@ -32328,6 +32355,9 @@
       <c r="N997" t="s">
         <v>1321</v>
       </c>
+      <c r="O997" t="s">
+        <v>1375</v>
+      </c>
     </row>
     <row r="998" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I998" s="2">
@@ -32348,6 +32378,9 @@
       </c>
       <c r="N998" t="s">
         <v>1322</v>
+      </c>
+      <c r="O998" t="s">
+        <v>1376</v>
       </c>
     </row>
     <row r="999" spans="1:15" x14ac:dyDescent="0.6">
@@ -32370,6 +32403,9 @@
       <c r="N999" t="s">
         <v>1323</v>
       </c>
+      <c r="O999" t="s">
+        <v>1377</v>
+      </c>
     </row>
     <row r="1000" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1000" s="2">
@@ -32390,6 +32426,9 @@
       </c>
       <c r="N1000" t="s">
         <v>1324</v>
+      </c>
+      <c r="O1000" t="s">
+        <v>1378</v>
       </c>
     </row>
     <row r="1001" spans="1:15" x14ac:dyDescent="0.6">
@@ -32412,6 +32451,9 @@
       <c r="N1001" t="s">
         <v>1322</v>
       </c>
+      <c r="O1001" t="s">
+        <v>1379</v>
+      </c>
     </row>
     <row r="1002" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1002" s="2">
@@ -32433,6 +32475,9 @@
       <c r="N1002" t="s">
         <v>1324</v>
       </c>
+      <c r="O1002" t="s">
+        <v>1380</v>
+      </c>
     </row>
     <row r="1003" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1003" s="2">
@@ -32454,6 +32499,9 @@
       <c r="N1003" t="s">
         <v>1323</v>
       </c>
+      <c r="O1003" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="1004" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1004" s="2">
@@ -32475,6 +32523,9 @@
       <c r="N1004" t="s">
         <v>150</v>
       </c>
+      <c r="O1004" t="s">
+        <v>1382</v>
+      </c>
     </row>
     <row r="1005" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1005" s="2">
@@ -32495,6 +32546,9 @@
       </c>
       <c r="N1005" t="s">
         <v>1321</v>
+      </c>
+      <c r="O1005" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="1006" spans="1:15" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7159BE93-D49E-4477-B1D0-2C51888C8756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5DBAD1-714E-44C4-AAAF-1FD894CFAAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4791" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="1457">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4990,6 +4990,10 @@
   </si>
   <si>
     <t>Set [1]</t>
+  </si>
+  <si>
+    <t>김윤중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6232,7 +6236,7 @@
         <v>778</v>
       </c>
       <c r="P22" t="s">
-        <v>433</v>
+        <v>1456</v>
       </c>
       <c r="Q22" t="s">
         <v>435</v>
@@ -6265,7 +6269,7 @@
         <v>779</v>
       </c>
       <c r="P23" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="Q23" t="s">
         <v>436</v>
@@ -6298,7 +6302,7 @@
         <v>780</v>
       </c>
       <c r="P24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q24" t="s">
         <v>437</v>
@@ -6350,7 +6354,7 @@
         <v>51</v>
       </c>
       <c r="P25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q25" t="s">
         <v>438</v>
@@ -6380,7 +6384,7 @@
         <v>52</v>
       </c>
       <c r="P26" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Q26" t="s">
         <v>439</v>
@@ -6410,7 +6414,7 @@
         <v>53</v>
       </c>
       <c r="P27" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q27" t="s">
         <v>440</v>
@@ -6440,7 +6444,7 @@
         <v>51</v>
       </c>
       <c r="P28" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Q28" t="s">
         <v>441</v>
@@ -6470,7 +6474,7 @@
         <v>52</v>
       </c>
       <c r="P29" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q29" t="s">
         <v>442</v>
@@ -6500,7 +6504,7 @@
         <v>53</v>
       </c>
       <c r="P30" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q30" t="s">
         <v>443</v>
@@ -6530,7 +6534,7 @@
         <v>51</v>
       </c>
       <c r="P31" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="Q31" t="s">
         <v>444</v>
@@ -6560,7 +6564,7 @@
         <v>53</v>
       </c>
       <c r="P32" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="Q32" t="s">
         <v>445</v>
@@ -6590,7 +6594,7 @@
         <v>52</v>
       </c>
       <c r="P33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q33" t="s">
         <v>446</v>
@@ -6648,7 +6652,7 @@
         <v>519</v>
       </c>
       <c r="P34" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q34" t="s">
         <v>447</v>
@@ -6681,7 +6685,7 @@
         <v>520</v>
       </c>
       <c r="P35" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="Q35" t="s">
         <v>448</v>
@@ -6714,7 +6718,7 @@
         <v>521</v>
       </c>
       <c r="P36" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="Q36" t="s">
         <v>449</v>
@@ -6747,7 +6751,7 @@
         <v>522</v>
       </c>
       <c r="P37" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="Q37" t="s">
         <v>450</v>
@@ -6780,7 +6784,7 @@
         <v>523</v>
       </c>
       <c r="P38" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="Q38" t="s">
         <v>451</v>
@@ -6811,6 +6815,15 @@
       </c>
       <c r="O39" t="s">
         <v>524</v>
+      </c>
+      <c r="P39" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1456</v>
+      </c>
+      <c r="R39" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5DBAD1-714E-44C4-AAAF-1FD894CFAAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4286D112-BB5E-4534-9E89-EE32F16DE77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1465">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4994,6 +4994,30 @@
   <si>
     <t>김윤중</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=i_nR85GdQ9CdSXAK&amp;t=730</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=_5ldIyXSjU_0SXsn&amp;t=1690</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=z33lGU_FaaiE0hSw&amp;t=2790</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=CVaRbtMLyjYRCZM2&amp;t=3370</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=AgX8ELm5Tf_ZE40S&amp;t=5020</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=0ArDRY_5vGSsNHxi&amp;t=6765</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=gZXbnOuAP0pcn1bm&amp;t=8745</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QiAUKSm59Z4?si=MdPuDtHaaekrsO4e&amp;t=7340</t>
   </si>
 </sst>
 </file>
@@ -33030,6 +33054,9 @@
       <c r="N1006" t="s">
         <v>1383</v>
       </c>
+      <c r="O1006" t="s">
+        <v>1457</v>
+      </c>
     </row>
     <row r="1007" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1007" s="2">
@@ -33051,6 +33078,9 @@
       <c r="N1007" t="s">
         <v>1384</v>
       </c>
+      <c r="O1007" t="s">
+        <v>1458</v>
+      </c>
     </row>
     <row r="1008" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1008" s="2">
@@ -33072,8 +33102,11 @@
       <c r="N1008" t="s">
         <v>1385</v>
       </c>
-    </row>
-    <row r="1009" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1008" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1009" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1009" s="2">
         <v>4</v>
       </c>
@@ -33093,8 +33126,11 @@
       <c r="N1009" t="s">
         <v>1386</v>
       </c>
-    </row>
-    <row r="1010" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1009" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1010" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1010" s="2">
         <v>5</v>
       </c>
@@ -33114,8 +33150,11 @@
       <c r="N1010" t="s">
         <v>1387</v>
       </c>
-    </row>
-    <row r="1011" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1010" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1011" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1011" s="2">
         <v>6</v>
       </c>
@@ -33135,8 +33174,11 @@
       <c r="N1011" t="s">
         <v>1381</v>
       </c>
-    </row>
-    <row r="1012" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1011" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1012" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1012" s="2">
         <v>7</v>
       </c>
@@ -33156,8 +33198,11 @@
       <c r="N1012" t="s">
         <v>1381</v>
       </c>
-    </row>
-    <row r="1013" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1012" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1013" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1013" s="2">
         <v>8</v>
       </c>
@@ -33177,68 +33222,71 @@
       <c r="N1013" t="s">
         <v>1385</v>
       </c>
-    </row>
-    <row r="1014" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1013" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1014" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1014" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1015" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1015" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1015" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1016" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1016" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1016" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1017" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1017" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1017" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1018" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1018" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1018" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1019" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1019" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1019" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1020" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1020" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1020" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1021" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1021" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1021" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1022" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1022" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1022" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1023" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1023" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1023" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1024" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1024" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1024" t="str">
         <f t="shared" si="19"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4286D112-BB5E-4534-9E89-EE32F16DE77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A4B4A-2988-40D8-BF4C-7E9FA3432F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4859" uniqueCount="1482">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5018,6 +5018,62 @@
   </si>
   <si>
     <t>https://youtu.be/QiAUKSm59Z4?si=MdPuDtHaaekrsO4e&amp;t=7340</t>
+  </si>
+  <si>
+    <t>2026.06.05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박하악</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚜비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵리나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[A]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=znS7AoN9UPD0mBep&amp;t=6774</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=L74M7Ta1MiksIBQ1&amp;t=7410</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=PFT6dJ_p6WqzTiUV&amp;t=8036</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=Zvx9AezyO0kXUDrk&amp;t=9328</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=pAfYibvhYDjEX5nq&amp;t=11340</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=0ADjQlaCaZSHGad5&amp;t=12272</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=BYyA8fU41EItqMzZ&amp;t=13985</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=7o4loUqeMsQ8XNX2&amp;t=15067</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=zC4FyTb3L075X8UF&amp;t=16610</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=3_YRWlKGkmhjoPxU&amp;t=17724</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=eZGfRZ6_7CawtoHy&amp;t=18648</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UEB_bv4CaEo?si=GOj3NgJPJ0YPafSM&amp;t=19252</t>
   </si>
 </sst>
 </file>
@@ -33106,7 +33162,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="1009" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1009" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1009" s="2">
         <v>4</v>
       </c>
@@ -33130,7 +33186,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="1010" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1010" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1010" s="2">
         <v>5</v>
       </c>
@@ -33154,7 +33210,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="1011" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1011" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1011" s="2">
         <v>6</v>
       </c>
@@ -33178,7 +33234,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="1012" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1012" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1012" s="2">
         <v>7</v>
       </c>
@@ -33202,7 +33258,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="1013" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1013" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1013" s="2">
         <v>8</v>
       </c>
@@ -33226,163 +33282,429 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="1014" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1014" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1014" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1014" t="str">
+        <f>IF(E1014&gt;F1014,"승",IF(E1014&lt;F1014,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E1014">
+        <f>COUNTIF(M1014:M1018,"승")</f>
+        <v>1</v>
+      </c>
+      <c r="F1014">
+        <f>COUNTA(M1014:M1018)-E1014</f>
+        <v>4</v>
+      </c>
+      <c r="G1014" s="1">
+        <f>E1014/(E1014+F1014)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I1014" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1014" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1014" t="s">
+        <v>17</v>
+      </c>
       <c r="L1014" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1015" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1014" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1014" t="s">
+        <v>1466</v>
+      </c>
+      <c r="O1014" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1015" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1015" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1015" t="s">
+        <v>66</v>
+      </c>
       <c r="L1015" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1016" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1015" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1015" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1015" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1016" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1016" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1016" t="s">
+        <v>16</v>
+      </c>
       <c r="L1016" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1017" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1016" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1016" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1016" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1017" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1017" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1017" t="s">
+        <v>25</v>
+      </c>
       <c r="L1017" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1018" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1017" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1017" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O1017" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1018" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1018" s="2">
+        <v>5</v>
+      </c>
+      <c r="K1018" t="s">
+        <v>25</v>
+      </c>
       <c r="L1018" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1019" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O1018" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1019" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1019" t="str">
+        <f>IF(E1019&gt;F1019,"승",IF(E1019&lt;F1019,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E1019">
+        <f>COUNTIF(M1019:M1025,"승")</f>
+        <v>4</v>
+      </c>
+      <c r="F1019">
+        <f>COUNTA(M1019:M1025)-E1019</f>
+        <v>3</v>
+      </c>
+      <c r="G1019" s="1">
+        <f>E1019/(E1019+F1019)</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I1019" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1019" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1019" t="s">
+        <v>16</v>
+      </c>
       <c r="L1019" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1020" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1019" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1019" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1019" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1020" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1020" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1020" t="s">
+        <v>25</v>
+      </c>
       <c r="L1020" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1021" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1020" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1020" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O1020" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1021" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1021" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1021" t="s">
+        <v>17</v>
+      </c>
       <c r="L1021" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1022" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1021" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1021" t="s">
+        <v>1466</v>
+      </c>
+      <c r="O1021" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1022" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1022" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1022" t="s">
+        <v>66</v>
+      </c>
       <c r="L1022" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1023" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1022" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1022" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1022" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1023" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1023" s="2">
+        <v>5</v>
+      </c>
+      <c r="K1023" t="s">
+        <v>66</v>
+      </c>
       <c r="L1023" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1024" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1023" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1023" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1023" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1024" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1024" s="2">
+        <v>6</v>
+      </c>
+      <c r="K1024" t="s">
+        <v>17</v>
+      </c>
       <c r="L1024" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1025" spans="12:12" x14ac:dyDescent="0.6">
+        <f t="shared" ref="L1024:L1025" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1024,$Q$2:$Q$99,0)),"")</f>
+        <v>T</v>
+      </c>
+      <c r="M1024" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1024" t="s">
+        <v>1466</v>
+      </c>
+      <c r="O1024" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1025" spans="9:15" x14ac:dyDescent="0.6">
+      <c r="I1025" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1025" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K1025" t="s">
+        <v>25</v>
+      </c>
       <c r="L1025" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1026" spans="12:12" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>T</v>
+      </c>
+      <c r="M1025" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1025" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O1025" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1026" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1026" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1027" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1027" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1027" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1028" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1028" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1028" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1029" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1029" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1029" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1030" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1030" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1030" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1031" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1031" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1031" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1032" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1032" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1032" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1033" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1033" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1033" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1034" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1034" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1034" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1035" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1035" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1035" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1036" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1036" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1036" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1037" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1037" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1037" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1038" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1038" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1038" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1039" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1039" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1039" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1040" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1040" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1040" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -33510,991 +33832,991 @@
     </row>
     <row r="1061" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1061" t="str">
-        <f t="shared" ref="L1061:L1124" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1061:L1124" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1062" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1062" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1063" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1063" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1064" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1064" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1065" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1065" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1066" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1066" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1067" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1067" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1068" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1068" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1069" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1069" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1070" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1070" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1071" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1071" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1072" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1072" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1073" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1073" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1074" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1074" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1075" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1075" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1076" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1076" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1077" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1077" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1078" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1078" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1079" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1079" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1080" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1080" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1081" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1081" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1082" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1082" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1083" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1083" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1084" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1084" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1085" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1085" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1086" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1086" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1087" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1087" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1088" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1088" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1089" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1089" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1090" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1090" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1091" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1091" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1092" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1092" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1093" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1093" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1094" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1094" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1095" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1095" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1096" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1096" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1097" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1097" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1098" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1098" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1099" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1099" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1100" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1100" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1101" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1101" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1102" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1102" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1103" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1103" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1104" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1104" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1105" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1105" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1106" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1106" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1107" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1107" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1108" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1108" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1109" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1109" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1110" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1110" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1111" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1111" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1112" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1112" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1113" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1113" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1114" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1114" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1115" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1115" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1116" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1116" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1117" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1117" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1118" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1118" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1119" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1119" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1120" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1120" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1121" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1121" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1122" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1122" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1123" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1123" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1124" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1124" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="1125" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1125" t="str">
-        <f t="shared" ref="L1125:L1188" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1125:L1188" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1126" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1126" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1127" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1127" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1128" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1128" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1129" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1129" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1130" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1130" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1131" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1131" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1132" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1132" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1133" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1133" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1134" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1134" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1135" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1135" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1136" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1136" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1137" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1137" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1138" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1138" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1139" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1139" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1140" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1140" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1141" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1141" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1142" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1142" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1143" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1143" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1144" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1144" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1145" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1145" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1146" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1146" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1147" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1147" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1148" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1148" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1149" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1149" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1150" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1150" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1151" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1151" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1152" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1152" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1153" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1153" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1154" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1154" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1155" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1155" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1156" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1156" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1157" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1157" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1158" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1158" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1159" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1159" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1160" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1160" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1161" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1161" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1162" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1162" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1163" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1163" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1164" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1164" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1165" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1165" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1166" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1166" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1167" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1167" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1168" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1168" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1169" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1169" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1170" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1170" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1171" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1171" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1172" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1172" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1173" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1173" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1174" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1174" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1175" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1175" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1176" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1176" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1177" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1177" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1178" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1178" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1179" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1179" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1180" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1180" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1181" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1181" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1182" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1182" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1183" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1183" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1184" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1184" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1185" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1185" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1186" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1186" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1187" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1187" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1188" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1188" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1189" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1189" t="str">
-        <f t="shared" ref="L1189:L1225" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1189:L1225" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1190" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1190" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1191" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1191" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1192" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1192" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1193" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1193" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1194" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1194" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1195" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1195" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1196" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1196" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1197" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1197" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1198" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1198" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1199" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1199" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1200" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1200" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1201" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1201" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1202" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1202" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1203" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1203" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1204" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1204" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1205" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1205" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1206" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1206" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1207" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1207" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1208" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1208" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1209" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1209" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1210" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1210" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1211" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1211" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1212" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1212" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1213" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1213" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1214" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1214" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1215" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1215" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1216" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1216" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1217" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1217" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1218" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1218" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1219" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1219" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1220" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1220" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1221" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1221" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1222" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1222" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1223" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1223" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1224" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1224" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1225" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1225" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A4B4A-2988-40D8-BF4C-7E9FA3432F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A421EBF9-5F0B-4589-B82B-611CF594FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4859" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4895" uniqueCount="1496">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5074,6 +5074,54 @@
   </si>
   <si>
     <t>https://youtu.be/UEB_bv4CaEo?si=GOj3NgJPJ0YPafSM&amp;t=19252</t>
+  </si>
+  <si>
+    <t>2026.06.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구보라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시녕뭉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하두링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제갈츄빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤하밍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=A7pZdTUPN_vSI5gF&amp;t=631</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=i_QvSsBXqj6NpnjO&amp;t=1783</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=nHZSExyPJ3e_J-IP&amp;t=2665</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=r8TXEg2B4TL52HkF&amp;t=4245</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=fKhrALRBKHfZ9VKS&amp;t=5318</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=b24s-Ui-W93Jh0gA&amp;t=6349</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=HfnXdkJ2qvfOyP_t&amp;t=7027</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7Zd42wicF4s?si=1CrZkh8DA3IVu40s&amp;t=8328</t>
   </si>
 </sst>
 </file>
@@ -33583,7 +33631,7 @@
         <v>17</v>
       </c>
       <c r="L1024" t="str">
-        <f t="shared" ref="L1024:L1025" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1024,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1024:L1030" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1024,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
       <c r="M1024" t="s">
@@ -33596,7 +33644,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1025" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1025" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1025" s="2">
         <v>7</v>
       </c>
@@ -33620,91 +33668,230 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="1026" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1026" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1026" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1026" t="str">
+        <f>IF(E1026&gt;F1026,"승",IF(E1026&lt;F1026,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E1026">
+        <f>COUNTIF(M1026:M1033,"승")</f>
+        <v>5</v>
+      </c>
+      <c r="F1026">
+        <f>COUNTA(M1026:M1033)-E1026</f>
+        <v>3</v>
+      </c>
+      <c r="G1026" s="1">
+        <f>E1026/(E1026+F1026)</f>
+        <v>0.625</v>
+      </c>
+      <c r="I1026" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1026" t="s">
+        <v>17</v>
+      </c>
       <c r="L1026" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1027" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>T</v>
+      </c>
+      <c r="M1026" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1026" t="s">
+        <v>1485</v>
+      </c>
+      <c r="O1026" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1027" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1027" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1027" t="s">
+        <v>19</v>
+      </c>
       <c r="L1027" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1028" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>P</v>
+      </c>
+      <c r="M1027" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1027" t="s">
+        <v>1487</v>
+      </c>
+      <c r="O1027" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1028" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1028" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1028" t="s">
+        <v>8</v>
+      </c>
       <c r="L1028" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1029" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>P</v>
+      </c>
+      <c r="M1028" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1028" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O1028" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1029" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1029" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1029" t="s">
+        <v>16</v>
+      </c>
       <c r="L1029" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1030" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>T</v>
+      </c>
+      <c r="M1029" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1029" t="s">
+        <v>1484</v>
+      </c>
+      <c r="O1029" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1030" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1030" s="2">
+        <v>5</v>
+      </c>
+      <c r="K1030" t="s">
+        <v>49</v>
+      </c>
       <c r="L1030" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1031" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="21"/>
+        <v>P</v>
+      </c>
+      <c r="M1030" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1030" t="s">
+        <v>1486</v>
+      </c>
+      <c r="O1030" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1031" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1031" s="2">
+        <v>6</v>
+      </c>
+      <c r="K1031" t="s">
+        <v>49</v>
+      </c>
       <c r="L1031" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1032" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" ref="L1031:L1033" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1031,$Q$2:$Q$99,0)),"")</f>
+        <v>P</v>
+      </c>
+      <c r="M1031" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1031" t="s">
+        <v>1486</v>
+      </c>
+      <c r="O1031" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1032" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1032" s="2">
+        <v>7</v>
+      </c>
+      <c r="K1032" t="s">
+        <v>17</v>
+      </c>
       <c r="L1032" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1033" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="M1032" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1032" t="s">
+        <v>1485</v>
+      </c>
+      <c r="O1032" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1033" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1033" s="2">
+        <v>8</v>
+      </c>
+      <c r="K1033" t="s">
+        <v>8</v>
+      </c>
       <c r="L1033" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1034" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1034" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1035" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1035" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1036" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1036" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1037" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1037" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1038" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1038" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1039" spans="9:15" x14ac:dyDescent="0.6">
+        <f t="shared" si="22"/>
+        <v>P</v>
+      </c>
+      <c r="M1033" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1033" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O1033" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:15" x14ac:dyDescent="0.6">
       <c r="L1039" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1040" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1040" spans="1:15" x14ac:dyDescent="0.6">
       <c r="L1040" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -33832,991 +34019,991 @@
     </row>
     <row r="1061" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1061" t="str">
-        <f t="shared" ref="L1061:L1124" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1061:L1124" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1062" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1062" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1063" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1063" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1064" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1064" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1065" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1065" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1066" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1066" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1067" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1067" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1068" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1068" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1069" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1069" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1070" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1070" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1071" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1071" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1072" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1072" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1073" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1073" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1074" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1074" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1075" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1075" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1076" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1076" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1077" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1077" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1078" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1078" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1079" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1079" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1080" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1080" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1081" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1081" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1082" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1082" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1083" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1083" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1084" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1084" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1085" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1085" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1086" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1086" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1087" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1087" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1088" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1088" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1089" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1089" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1090" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1090" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1091" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1091" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1092" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1092" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1093" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1093" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1094" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1094" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1095" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1095" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1096" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1096" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1097" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1097" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1098" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1098" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1099" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1099" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1100" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1100" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1101" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1101" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1102" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1102" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1103" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1103" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1104" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1104" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1105" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1105" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1106" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1106" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1107" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1107" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1108" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1108" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1109" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1109" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1110" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1110" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1111" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1111" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1112" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1112" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1113" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1113" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1114" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1114" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1115" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1115" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1116" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1116" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1117" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1117" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1118" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1118" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1119" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1119" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1120" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1120" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1121" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1121" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1122" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1122" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1123" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1123" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1124" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1124" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="1125" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1125" t="str">
-        <f t="shared" ref="L1125:L1188" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1125:L1188" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1126" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1126" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1127" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1127" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1128" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1128" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1129" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1129" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1130" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1130" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1131" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1131" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1132" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1132" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1133" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1133" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1134" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1134" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1135" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1135" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1136" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1136" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1137" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1137" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1138" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1138" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1139" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1139" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1140" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1140" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1141" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1141" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1142" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1142" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1143" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1143" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1144" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1144" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1145" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1145" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1146" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1146" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1147" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1147" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1148" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1148" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1149" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1149" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1150" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1150" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1151" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1151" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1152" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1152" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1153" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1153" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1154" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1154" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1155" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1155" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1156" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1156" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1157" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1157" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1158" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1158" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1159" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1159" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1160" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1160" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1161" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1161" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1162" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1162" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1163" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1163" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1164" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1164" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1165" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1165" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1166" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1166" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1167" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1167" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1168" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1168" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1169" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1169" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1170" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1170" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1171" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1171" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1172" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1172" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1173" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1173" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1174" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1174" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1175" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1175" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1176" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1176" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1177" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1177" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1178" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1178" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1179" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1179" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1180" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1180" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1181" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1181" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1182" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1182" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1183" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1183" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1184" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1184" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1185" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1185" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1186" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1186" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1187" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1187" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1188" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1188" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1189" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1189" t="str">
-        <f t="shared" ref="L1189:L1225" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1189:L1225" si="25">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1190" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1190" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1191" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1191" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1192" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1192" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1193" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1193" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1194" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1194" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1195" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1195" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1196" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1196" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1197" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1197" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1198" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1198" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1199" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1199" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1200" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1200" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1201" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1201" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1202" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1202" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1203" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1203" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1204" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1204" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1205" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1205" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1206" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1206" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1207" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1207" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1208" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1208" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1209" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1209" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1210" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1210" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1211" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1211" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1212" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1212" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1213" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1213" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1214" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1214" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1215" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1215" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1216" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1216" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1217" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1217" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1218" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1218" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1219" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1219" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1220" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1220" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1221" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1221" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1222" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1222" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1223" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1223" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1224" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1224" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1225" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1225" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A421EBF9-5F0B-4589-B82B-611CF594FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEACDC00-D7AE-40CC-8B77-E0CE232EBCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -33342,19 +33342,19 @@
       </c>
       <c r="D1014" t="str">
         <f>IF(E1014&gt;F1014,"승",IF(E1014&lt;F1014,"패"))</f>
-        <v>패</v>
+        <v>승</v>
       </c>
       <c r="E1014">
-        <f>COUNTIF(M1014:M1018,"승")</f>
-        <v>1</v>
+        <f>COUNTIF(M1014:M1020,"승")</f>
+        <v>4</v>
       </c>
       <c r="F1014">
-        <f>COUNTA(M1014:M1018)-E1014</f>
-        <v>4</v>
+        <f>COUNTA(M1014:M1020)-E1014</f>
+        <v>3</v>
       </c>
       <c r="G1014" s="1">
         <f>E1014/(E1014+F1014)</f>
-        <v>0.2</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I1014" s="2">
         <v>1</v>
@@ -33363,20 +33363,20 @@
         <v>1455</v>
       </c>
       <c r="K1014" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L1014" t="str">
         <f t="shared" si="19"/>
         <v>T</v>
       </c>
       <c r="M1014" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1014" t="s">
-        <v>1466</v>
+        <v>72</v>
       </c>
       <c r="O1014" t="s">
-        <v>1470</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1015" spans="1:15" x14ac:dyDescent="0.6">
@@ -33387,20 +33387,20 @@
         <v>2</v>
       </c>
       <c r="K1015" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="L1015" t="str">
         <f t="shared" si="19"/>
-        <v>Z</v>
+        <v>T</v>
       </c>
       <c r="M1015" t="s">
         <v>3</v>
       </c>
       <c r="N1015" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="O1015" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1016" spans="1:15" x14ac:dyDescent="0.6">
@@ -33411,7 +33411,7 @@
         <v>3</v>
       </c>
       <c r="K1016" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L1016" t="str">
         <f t="shared" si="19"/>
@@ -33421,10 +33421,10 @@
         <v>4</v>
       </c>
       <c r="N1016" t="s">
-        <v>72</v>
+        <v>1466</v>
       </c>
       <c r="O1016" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1017" spans="1:15" x14ac:dyDescent="0.6">
@@ -33435,20 +33435,20 @@
         <v>4</v>
       </c>
       <c r="K1017" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L1017" t="str">
         <f t="shared" si="19"/>
-        <v>T</v>
+        <v>Z</v>
       </c>
       <c r="M1017" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1017" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="O1017" t="s">
-        <v>1473</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1018" spans="1:15" x14ac:dyDescent="0.6">
@@ -33459,83 +33459,58 @@
         <v>5</v>
       </c>
       <c r="K1018" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L1018" t="str">
         <f t="shared" si="19"/>
+        <v>Z</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1018" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1019" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1019" s="2">
+        <v>6</v>
+      </c>
+      <c r="K1019" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1019" t="str">
+        <f t="shared" ref="L1019:L1030" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1019,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
-      <c r="M1018" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1018" t="s">
-        <v>1468</v>
-      </c>
-      <c r="O1018" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="1019" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="A1019" t="s">
-        <v>1465</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1019" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1019" t="str">
-        <f>IF(E1019&gt;F1019,"승",IF(E1019&lt;F1019,"패"))</f>
-        <v>승</v>
-      </c>
-      <c r="E1019">
-        <f>COUNTIF(M1019:M1025,"승")</f>
-        <v>4</v>
-      </c>
-      <c r="F1019">
-        <f>COUNTA(M1019:M1025)-E1019</f>
-        <v>3</v>
-      </c>
-      <c r="G1019" s="1">
-        <f>E1019/(E1019+F1019)</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="I1019" s="2">
-        <v>1</v>
-      </c>
-      <c r="J1019" t="s">
-        <v>1455</v>
-      </c>
-      <c r="K1019" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1019" t="str">
-        <f t="shared" si="19"/>
-        <v>T</v>
-      </c>
       <c r="M1019" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1019" t="s">
-        <v>72</v>
+        <v>1466</v>
       </c>
       <c r="O1019" t="s">
-        <v>1475</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1020" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1020" s="2">
-        <v>2</v>
-      </c>
-      <c r="J1020" s="2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J1020" s="2" t="s">
+        <v>1469</v>
       </c>
       <c r="K1020" t="s">
         <v>25</v>
       </c>
       <c r="L1020" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>T</v>
       </c>
       <c r="M1020" t="s">
@@ -33545,21 +33520,46 @@
         <v>1468</v>
       </c>
       <c r="O1020" t="s">
-        <v>1476</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1021" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1021" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1021" t="str">
+        <f>IF(E1021&gt;F1021,"승",IF(E1021&lt;F1021,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E1021">
+        <f>COUNTIF(M1021:M1025,"승")</f>
+        <v>1</v>
+      </c>
+      <c r="F1021">
+        <f>COUNTA(M1021:M1025)-E1021</f>
+        <v>4</v>
+      </c>
+      <c r="G1021" s="1">
+        <f>E1021/(E1021+F1021)</f>
+        <v>0.2</v>
+      </c>
       <c r="I1021" s="2">
-        <v>3</v>
-      </c>
-      <c r="J1021" s="2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J1021" t="s">
+        <v>1455</v>
       </c>
       <c r="K1021" t="s">
         <v>17</v>
       </c>
       <c r="L1021" t="str">
-        <f t="shared" si="19"/>
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1021,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
       <c r="M1021" t="s">
@@ -33569,21 +33569,21 @@
         <v>1466</v>
       </c>
       <c r="O1021" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1022" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1022" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J1022" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1022" t="s">
         <v>66</v>
       </c>
       <c r="L1022" t="str">
-        <f t="shared" si="19"/>
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1022,$Q$2:$Q$99,0)),"")</f>
         <v>Z</v>
       </c>
       <c r="M1022" t="s">
@@ -33593,79 +33593,79 @@
         <v>1467</v>
       </c>
       <c r="O1022" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1023" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1023" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J1023" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1023" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="L1023" t="str">
-        <f t="shared" si="19"/>
-        <v>Z</v>
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1023,$Q$2:$Q$99,0)),"")</f>
+        <v>T</v>
       </c>
       <c r="M1023" t="s">
         <v>4</v>
       </c>
       <c r="N1023" t="s">
-        <v>1467</v>
+        <v>72</v>
       </c>
       <c r="O1023" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1024" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1024" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J1024" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K1024" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L1024" t="str">
-        <f t="shared" ref="L1024:L1030" si="21">IFERROR(INDEX($R$2:$R$99,MATCH(K1024,$Q$2:$Q$99,0)),"")</f>
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1024,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
       <c r="M1024" t="s">
         <v>4</v>
       </c>
       <c r="N1024" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="O1024" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1025" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1025" s="2">
-        <v>7</v>
-      </c>
-      <c r="J1025" s="2" t="s">
-        <v>1469</v>
+        <v>5</v>
+      </c>
+      <c r="J1025" s="2">
+        <v>5</v>
       </c>
       <c r="K1025" t="s">
         <v>25</v>
       </c>
       <c r="L1025" t="str">
-        <f t="shared" si="21"/>
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1025,$Q$2:$Q$99,0)),"")</f>
         <v>T</v>
       </c>
       <c r="M1025" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1025" t="s">
         <v>1468</v>
       </c>
       <c r="O1025" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1026" spans="1:15" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEACDC00-D7AE-40CC-8B77-E0CE232EBCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E45762-42BF-4503-BA77-EBD629CCCFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4895" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="1500">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5043,9 +5043,6 @@
     <t>https://youtu.be/UEB_bv4CaEo?si=znS7AoN9UPD0mBep&amp;t=6774</t>
   </si>
   <si>
-    <t>https://youtu.be/UEB_bv4CaEo?si=L74M7Ta1MiksIBQ1&amp;t=7410</t>
-  </si>
-  <si>
     <t>https://youtu.be/UEB_bv4CaEo?si=PFT6dJ_p6WqzTiUV&amp;t=8036</t>
   </si>
   <si>
@@ -5122,6 +5119,26 @@
   </si>
   <si>
     <t>https://youtu.be/7Zd42wicF4s?si=1CrZkh8DA3IVu40s&amp;t=8328</t>
+  </si>
+  <si>
+    <t>설둥이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연블비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.06.07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -33376,7 +33393,7 @@
         <v>72</v>
       </c>
       <c r="O1014" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1015" spans="1:15" x14ac:dyDescent="0.6">
@@ -33400,7 +33417,7 @@
         <v>1468</v>
       </c>
       <c r="O1015" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1016" spans="1:15" x14ac:dyDescent="0.6">
@@ -33424,7 +33441,7 @@
         <v>1466</v>
       </c>
       <c r="O1016" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1017" spans="1:15" x14ac:dyDescent="0.6">
@@ -33448,7 +33465,7 @@
         <v>1467</v>
       </c>
       <c r="O1017" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1018" spans="1:15" x14ac:dyDescent="0.6">
@@ -33472,7 +33489,7 @@
         <v>1467</v>
       </c>
       <c r="O1018" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1019" spans="1:15" x14ac:dyDescent="0.6">
@@ -33496,7 +33513,7 @@
         <v>1466</v>
       </c>
       <c r="O1019" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1020" spans="1:15" x14ac:dyDescent="0.6">
@@ -33520,7 +33537,7 @@
         <v>1468</v>
       </c>
       <c r="O1020" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1021" spans="1:15" x14ac:dyDescent="0.6">
@@ -33593,7 +33610,7 @@
         <v>1467</v>
       </c>
       <c r="O1022" t="s">
-        <v>1471</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1023" spans="1:15" x14ac:dyDescent="0.6">
@@ -33617,7 +33634,7 @@
         <v>72</v>
       </c>
       <c r="O1023" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1024" spans="1:15" x14ac:dyDescent="0.6">
@@ -33641,7 +33658,7 @@
         <v>1468</v>
       </c>
       <c r="O1024" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1025" spans="1:15" x14ac:dyDescent="0.6">
@@ -33665,12 +33682,12 @@
         <v>1468</v>
       </c>
       <c r="O1025" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1026" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A1026" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1026" t="s">
         <v>23</v>
@@ -33711,10 +33728,10 @@
         <v>4</v>
       </c>
       <c r="N1026" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="O1026" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1027" spans="1:15" x14ac:dyDescent="0.6">
@@ -33735,10 +33752,10 @@
         <v>3</v>
       </c>
       <c r="N1027" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="O1027" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1028" spans="1:15" x14ac:dyDescent="0.6">
@@ -33759,10 +33776,10 @@
         <v>3</v>
       </c>
       <c r="N1028" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="O1028" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1029" spans="1:15" x14ac:dyDescent="0.6">
@@ -33783,10 +33800,10 @@
         <v>4</v>
       </c>
       <c r="N1029" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="O1029" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1030" spans="1:15" x14ac:dyDescent="0.6">
@@ -33807,10 +33824,10 @@
         <v>3</v>
       </c>
       <c r="N1030" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="O1030" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1031" spans="1:15" x14ac:dyDescent="0.6">
@@ -33824,17 +33841,17 @@
         <v>49</v>
       </c>
       <c r="L1031" t="str">
-        <f t="shared" ref="L1031:L1033" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1031,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1031:L1037" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1031,$Q$2:$Q$99,0)),"")</f>
         <v>P</v>
       </c>
       <c r="M1031" t="s">
         <v>3</v>
       </c>
       <c r="N1031" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="O1031" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1032" spans="1:15" x14ac:dyDescent="0.6">
@@ -33855,10 +33872,10 @@
         <v>4</v>
       </c>
       <c r="N1032" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="O1032" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1033" spans="1:15" x14ac:dyDescent="0.6">
@@ -33879,10 +33896,119 @@
         <v>3</v>
       </c>
       <c r="N1033" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="O1033" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1034" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1034" t="str">
+        <f>IF(E1034&gt;F1034,"승",IF(E1034&lt;F1034,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E1034">
+        <f>COUNTIF(M1034:M1037,"승")</f>
+        <v>3</v>
+      </c>
+      <c r="F1034">
+        <f>COUNTA(M1034:M1037)-E1034</f>
+        <v>1</v>
+      </c>
+      <c r="G1034" s="1">
+        <f>E1034/(E1034+F1034)</f>
+        <v>0.75</v>
+      </c>
+      <c r="I1034" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1034" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1034" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1034" t="str">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="M1034" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1034" t="s">
         <v>1495</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1035" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1035" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1035" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1035" t="str">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="M1035" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1035" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1036" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1036" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1036" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1036" t="str">
+        <f t="shared" si="22"/>
+        <v>P</v>
+      </c>
+      <c r="M1036" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1036" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1037" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1037" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1037" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1037" t="str">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="M1037" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1037" t="s">
+        <v>1496</v>
       </c>
     </row>
     <row r="1039" spans="1:15" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E45762-42BF-4503-BA77-EBD629CCCFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF697C65-A9DB-45C7-ABFE-673A7DCC768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4915" uniqueCount="1504">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5139,6 +5139,18 @@
   <si>
     <t>ㄴ</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/vFiLWz8gjPc?si=tRdRfPYFH7WwaFFZ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vFiLWz8gjPc?si=xGuONO9HrJATxS4l&amp;t=7528</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vFiLWz8gjPc?si=JPHQeFlTuY_GZOtX&amp;t=8655</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vFiLWz8gjPc?si=HmripkPZ8LNP7YOX&amp;t=9266</t>
   </si>
 </sst>
 </file>
@@ -33947,6 +33959,9 @@
       <c r="N1034" t="s">
         <v>1495</v>
       </c>
+      <c r="O1034" t="s">
+        <v>1500</v>
+      </c>
     </row>
     <row r="1035" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1035" s="2">
@@ -33968,6 +33983,9 @@
       <c r="N1035" t="s">
         <v>1496</v>
       </c>
+      <c r="O1035" t="s">
+        <v>1501</v>
+      </c>
     </row>
     <row r="1036" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1036" s="2">
@@ -33988,6 +34006,9 @@
       </c>
       <c r="N1036" t="s">
         <v>1497</v>
+      </c>
+      <c r="O1036" t="s">
+        <v>1502</v>
       </c>
     </row>
     <row r="1037" spans="1:15" x14ac:dyDescent="0.6">
@@ -34009,6 +34030,9 @@
       </c>
       <c r="N1037" t="s">
         <v>1496</v>
+      </c>
+      <c r="O1037" t="s">
+        <v>1503</v>
       </c>
     </row>
     <row r="1039" spans="1:15" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF697C65-A9DB-45C7-ABFE-673A7DCC768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF5CCC1-3765-4519-AB52-0D0B50994EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4915" uniqueCount="1504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4948" uniqueCount="1511">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5151,6 +5151,34 @@
   </si>
   <si>
     <t>https://youtu.be/vFiLWz8gjPc?si=HmripkPZ8LNP7YOX&amp;t=9266</t>
+  </si>
+  <si>
+    <t>DM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다뉴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수니양</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵리나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김말랑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -33853,7 +33881,7 @@
         <v>49</v>
       </c>
       <c r="L1031" t="str">
-        <f t="shared" ref="L1031:L1037" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1031,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1031:L1038" si="22">IFERROR(INDEX($R$2:$R$99,MATCH(K1031,$Q$2:$Q$99,0)),"")</f>
         <v>P</v>
       </c>
       <c r="M1031" t="s">
@@ -34035,109 +34063,278 @@
         <v>1503</v>
       </c>
     </row>
+    <row r="1038" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1038" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1038" t="str">
+        <f>IF(E1038&gt;F1038,"승",IF(E1038&lt;F1038,"패"))</f>
+        <v>승</v>
+      </c>
+      <c r="E1038">
+        <f>COUNTIF(M1038:M1046,"승")</f>
+        <v>6</v>
+      </c>
+      <c r="F1038">
+        <f>COUNTA(M1038:M1046)-E1038</f>
+        <v>3</v>
+      </c>
+      <c r="G1038" s="1">
+        <f>E1038/(E1038+F1038)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H1038" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1038" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1038" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1038" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1038" t="str">
+        <f t="shared" si="22"/>
+        <v>Z</v>
+      </c>
+      <c r="M1038" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1038" t="s">
+        <v>1505</v>
+      </c>
+    </row>
     <row r="1039" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1039" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1039" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1039" t="s">
+        <v>49</v>
+      </c>
       <c r="L1039" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>P</v>
+      </c>
+      <c r="M1039" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1039" t="s">
+        <v>1506</v>
       </c>
     </row>
     <row r="1040" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1040" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1040" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1040" t="s">
+        <v>25</v>
+      </c>
       <c r="L1040" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1041" spans="12:12" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1040" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1040" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1041" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1041" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1041" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1041" t="s">
+        <v>19</v>
+      </c>
       <c r="L1041" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1042" spans="12:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M1041" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1041" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1042" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1042" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1042" t="s">
+        <v>18</v>
+      </c>
       <c r="L1042" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1043" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1042" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1042" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1043" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1043" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1043" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1043" t="s">
+        <v>19</v>
+      </c>
       <c r="L1043" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1044" spans="12:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M1043" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1043" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1044" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1044" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1044" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1044" t="s">
+        <v>25</v>
+      </c>
       <c r="L1044" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1045" spans="12:12" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1044" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1044" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1045" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1045" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1045" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1045" t="s">
+        <v>49</v>
+      </c>
       <c r="L1045" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1046" spans="12:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M1045" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1045" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1046" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1046" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1046" s="2">
+        <v>5</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>39</v>
+      </c>
       <c r="L1046" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1047" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1046" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1047" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1047" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1048" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1048" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1048" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1049" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1049" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1049" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1050" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1050" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1050" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1051" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1051" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1051" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1052" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1052" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1052" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1053" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1053" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1053" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1054" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1054" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1054" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1055" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1055" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1055" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1056" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1056" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1056" t="str">
         <f t="shared" si="19"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF5CCC1-3765-4519-AB52-0D0B50994EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6436D498-BE51-4AAF-9A35-202DFEC437B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4948" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="1520">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5179,6 +5179,34 @@
   <si>
     <t>김말랑</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=R794HzgDDlOf8tFq&amp;t=3745</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=l8j3xrtXm37OqZvN&amp;t=4725</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=cjOFngoXli_4e6eJ&amp;t=6579</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=u-BZNur9r7-vY8iq&amp;t=6090</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=RmAYXkoiPqGD4lUB&amp;t=7272</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=CFsoENVojhEnYug4&amp;t=8389</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=UbaI4st2fA4eyham&amp;t=9682</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=m9ghI-ea0v563qo-&amp;t=10915</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mnRmUqqE4U?si=I9S89eNnPD0gC4wr&amp;t=11803</t>
   </si>
 </sst>
 </file>
@@ -34111,6 +34139,9 @@
       <c r="N1038" t="s">
         <v>1505</v>
       </c>
+      <c r="O1038" t="s">
+        <v>1511</v>
+      </c>
     </row>
     <row r="1039" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1039" s="2">
@@ -34131,6 +34162,9 @@
       </c>
       <c r="N1039" t="s">
         <v>1506</v>
+      </c>
+      <c r="O1039" t="s">
+        <v>1512</v>
       </c>
     </row>
     <row r="1040" spans="1:15" x14ac:dyDescent="0.6">
@@ -34153,8 +34187,11 @@
       <c r="N1040" t="s">
         <v>1509</v>
       </c>
-    </row>
-    <row r="1041" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1040" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1041" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1041" s="2">
         <v>4</v>
       </c>
@@ -34174,8 +34211,11 @@
       <c r="N1041" t="s">
         <v>1507</v>
       </c>
-    </row>
-    <row r="1042" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1041" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1042" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1042" s="2">
         <v>5</v>
       </c>
@@ -34195,8 +34235,11 @@
       <c r="N1042" t="s">
         <v>1508</v>
       </c>
-    </row>
-    <row r="1043" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1042" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1043" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1043" s="2">
         <v>6</v>
       </c>
@@ -34216,8 +34259,11 @@
       <c r="N1043" t="s">
         <v>1507</v>
       </c>
-    </row>
-    <row r="1044" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1043" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1044" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1044" s="2">
         <v>7</v>
       </c>
@@ -34237,8 +34283,11 @@
       <c r="N1044" t="s">
         <v>1509</v>
       </c>
-    </row>
-    <row r="1045" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1044" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1045" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1045" s="2">
         <v>8</v>
       </c>
@@ -34258,8 +34307,11 @@
       <c r="N1045" t="s">
         <v>1510</v>
       </c>
-    </row>
-    <row r="1046" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1045" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1046" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1046" s="2">
         <v>9</v>
       </c>
@@ -34279,62 +34331,65 @@
       <c r="N1046" t="s">
         <v>1505</v>
       </c>
-    </row>
-    <row r="1047" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1046" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1047" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1047" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1048" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1048" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1048" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1049" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1049" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1049" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1050" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1050" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1050" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1051" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1051" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1051" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1052" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1052" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1052" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1053" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1053" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1053" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1054" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1054" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1054" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1055" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1055" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1055" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1056" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1056" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1056" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -35357,6 +35412,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6436D498-BE51-4AAF-9A35-202DFEC437B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3016D6A6-E1AF-46FF-B42D-7B0F5DE9F79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="1520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="1521">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5207,6 +5207,10 @@
   </si>
   <si>
     <t>https://youtu.be/0mnRmUqqE4U?si=I9S89eNnPD0gC4wr&amp;t=11803</t>
+  </si>
+  <si>
+    <t>2026.06.09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -34093,7 +34097,7 @@
     </row>
     <row r="1038" spans="1:15" x14ac:dyDescent="0.6">
       <c r="A1038" t="s">
-        <v>1498</v>
+        <v>1520</v>
       </c>
       <c r="B1038" t="s">
         <v>1504</v>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3016D6A6-E1AF-46FF-B42D-7B0F5DE9F79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7F0DC2-FC5D-4F96-8CAD-43A41B7A9CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="1529">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5210,6 +5210,38 @@
   </si>
   <si>
     <t>2026.06.09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.06.10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤요이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2라니</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주서리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>치리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>깨림이</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -34195,7 +34227,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="1041" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1041" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1041" s="2">
         <v>4</v>
       </c>
@@ -34219,7 +34251,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="1042" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1042" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1042" s="2">
         <v>5</v>
       </c>
@@ -34243,7 +34275,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="1043" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1043" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1043" s="2">
         <v>6</v>
       </c>
@@ -34267,7 +34299,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="1044" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1044" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1044" s="2">
         <v>7</v>
       </c>
@@ -34291,7 +34323,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="1045" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1045" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1045" s="2">
         <v>8</v>
       </c>
@@ -34315,7 +34347,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="1046" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1046" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1046" s="2">
         <v>9</v>
       </c>
@@ -34339,61 +34371,188 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="1047" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1047" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1047" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1047" t="str">
+        <f>IF(E1047&gt;F1047,"승",IF(E1047&lt;F1047,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E1047">
+        <f>COUNTIF(M1047:M1053,"승")</f>
+        <v>3</v>
+      </c>
+      <c r="F1047">
+        <f>COUNTA(M1047:M1053)-E1047</f>
+        <v>4</v>
+      </c>
+      <c r="G1047" s="1">
+        <f>E1047/(E1047+F1047)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H1047" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1047" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1047" t="s">
+        <v>19</v>
+      </c>
       <c r="L1047" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1048" spans="9:15" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M1047" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1047" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1048" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1048" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1048" t="s">
+        <v>17</v>
+      </c>
       <c r="L1048" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1049" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1048" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1048" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1049" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1049" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1049" t="s">
+        <v>1525</v>
+      </c>
       <c r="L1049" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1050" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1049" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1049" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1050" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1050" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1050" t="s">
+        <v>1526</v>
+      </c>
       <c r="L1050" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1051" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1050" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1050" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1051" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1051" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1051" t="s">
+        <v>16</v>
+      </c>
       <c r="L1051" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1052" spans="9:15" x14ac:dyDescent="0.6">
+        <v>T</v>
+      </c>
+      <c r="M1051" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1051" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1052" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1052" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1052" t="s">
+        <v>66</v>
+      </c>
       <c r="L1052" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1053" spans="9:15" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1052" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1052" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1053" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1053" t="s">
+        <v>557</v>
+      </c>
+      <c r="K1053" t="s">
+        <v>19</v>
+      </c>
       <c r="L1053" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1054" spans="9:15" x14ac:dyDescent="0.6">
-      <c r="L1054" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1055" spans="9:15" x14ac:dyDescent="0.6">
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1053,$Q$2:$Q$99,0)),"")</f>
+        <v>P</v>
+      </c>
+      <c r="M1053" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1053" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:15" x14ac:dyDescent="0.6">
       <c r="L1055" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="1056" spans="9:15" x14ac:dyDescent="0.6">
+    <row r="1056" spans="1:15" x14ac:dyDescent="0.6">
       <c r="L1056" t="str">
         <f t="shared" si="19"/>
         <v/>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7F0DC2-FC5D-4F96-8CAD-43A41B7A9CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974380BF-FE91-4008-8FD6-00FD6AD33DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
+    <workbookView xWindow="19935" yWindow="33585" windowWidth="21600" windowHeight="16065" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="1536">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5243,6 +5243,27 @@
   <si>
     <t>깨림이</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=cuGWdzfsW35Tcwca&amp;t=3620</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=3o0caOhRUfm8XLEh&amp;t=4876</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=C50pGE-zgYyYs9Af&amp;t=6009</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=F7BSF5dr9hU9HYTL&amp;t=7155</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=0xflW3nBx_2Tfx3X&amp;t=8100</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=SrBf3UxWWmkPCUh6&amp;t=9069</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qx4jkm3q-ss?si=ST6oFSp_K_LwWSGt&amp;t=10630</t>
   </si>
 </sst>
 </file>
@@ -34419,6 +34440,9 @@
       <c r="N1047" t="s">
         <v>1522</v>
       </c>
+      <c r="O1047" t="s">
+        <v>1529</v>
+      </c>
     </row>
     <row r="1048" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1048" s="2">
@@ -34440,6 +34464,9 @@
       <c r="N1048" t="s">
         <v>1523</v>
       </c>
+      <c r="O1048" t="s">
+        <v>1530</v>
+      </c>
     </row>
     <row r="1049" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1049" s="2">
@@ -34461,6 +34488,9 @@
       <c r="N1049" t="s">
         <v>1528</v>
       </c>
+      <c r="O1049" t="s">
+        <v>1531</v>
+      </c>
     </row>
     <row r="1050" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1050" s="2">
@@ -34481,6 +34511,9 @@
       </c>
       <c r="N1050" t="s">
         <v>1527</v>
+      </c>
+      <c r="O1050" t="s">
+        <v>1532</v>
       </c>
     </row>
     <row r="1051" spans="1:15" x14ac:dyDescent="0.6">
@@ -34503,6 +34536,9 @@
       <c r="N1051" t="s">
         <v>1524</v>
       </c>
+      <c r="O1051" t="s">
+        <v>1533</v>
+      </c>
     </row>
     <row r="1052" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1052" s="2">
@@ -34524,6 +34560,9 @@
       <c r="N1052" t="s">
         <v>1528</v>
       </c>
+      <c r="O1052" t="s">
+        <v>1534</v>
+      </c>
     </row>
     <row r="1053" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1053" s="2">
@@ -34544,6 +34583,9 @@
       </c>
       <c r="N1053" t="s">
         <v>1522</v>
+      </c>
+      <c r="O1053" t="s">
+        <v>1535</v>
       </c>
     </row>
     <row r="1055" spans="1:15" x14ac:dyDescent="0.6">

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974380BF-FE91-4008-8FD6-00FD6AD33DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47749F2F-D755-4E66-AB1B-7CD193309FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19935" yWindow="33585" windowWidth="21600" windowHeight="16065" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
+    <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="1536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="1543">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5264,6 +5264,34 @@
   </si>
   <si>
     <t>https://youtu.be/Qx4jkm3q-ss?si=ST6oFSp_K_LwWSGt&amp;t=10630</t>
+  </si>
+  <si>
+    <t>2026.06.11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚜미</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경콩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>갱이다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김유나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -34588,1029 +34616,1183 @@
         <v>1535</v>
       </c>
     </row>
+    <row r="1054" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="A1054" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1054" t="str">
+        <f>IF(E1054&gt;F1054,"승",IF(E1054&lt;F1054,"패"))</f>
+        <v>패</v>
+      </c>
+      <c r="E1054">
+        <f>COUNTIF(M1054:M1061,"승")</f>
+        <v>2</v>
+      </c>
+      <c r="F1054">
+        <f>COUNTA(M1054:M1061)-E1054</f>
+        <v>6</v>
+      </c>
+      <c r="G1054" s="1">
+        <f>E1054/(E1054+F1054)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H1054" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1054" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1054" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1054" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1054" t="str">
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1054,$Q$2:$Q$99,0)),"")</f>
+        <v>P</v>
+      </c>
+      <c r="M1054" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1054" t="s">
+        <v>1538</v>
+      </c>
+    </row>
     <row r="1055" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1055" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1055" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1055" t="s">
+        <v>1537</v>
+      </c>
       <c r="L1055" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Z</v>
+      </c>
+      <c r="M1055" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1055" t="s">
+        <v>1539</v>
       </c>
     </row>
     <row r="1056" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="I1056" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1056" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1056" t="s">
+        <v>66</v>
+      </c>
       <c r="L1056" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1057" spans="12:12" x14ac:dyDescent="0.6">
+        <v>Z</v>
+      </c>
+      <c r="M1056" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1056" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1057" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1057" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1057" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K1057" t="s">
+        <v>49</v>
+      </c>
       <c r="L1057" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1058" spans="12:12" x14ac:dyDescent="0.6">
+        <v>P</v>
+      </c>
+      <c r="M1057" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1057" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1058" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1058" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1058" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1058" t="s">
+        <v>19</v>
+      </c>
       <c r="L1058" t="str">
         <f t="shared" si="19"/>
+        <v>P</v>
+      </c>
+      <c r="M1058" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1058" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1059" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1059" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1059" s="2">
+        <v>3</v>
+      </c>
+      <c r="K1059" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1059" t="str">
+        <f t="shared" ref="L1059:L1060" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1059,$Q$2:$Q$99,0)),"")</f>
+        <v>Z</v>
+      </c>
+      <c r="M1059" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1059" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1060" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1060" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1060" s="2">
+        <v>4</v>
+      </c>
+      <c r="K1060" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L1060" t="str">
+        <f t="shared" si="23"/>
+        <v>Z</v>
+      </c>
+      <c r="M1060" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1060" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1061" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="I1061" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1061" s="2">
+        <v>5</v>
+      </c>
+      <c r="K1061" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1061" t="str">
+        <f>IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
+        <v>P</v>
+      </c>
+      <c r="M1061" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1061" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1062" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1062" t="str">
+        <f t="shared" ref="L1061:L1124" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1062,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="1059" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1059" t="str">
-        <f t="shared" si="19"/>
+    <row r="1063" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1063" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1060" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1060" t="str">
-        <f t="shared" si="19"/>
+    <row r="1064" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1064" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1061" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1061" t="str">
-        <f t="shared" ref="L1061:L1124" si="23">IFERROR(INDEX($R$2:$R$99,MATCH(K1061,$Q$2:$Q$99,0)),"")</f>
+    <row r="1065" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1065" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1062" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1062" t="str">
-        <f t="shared" si="23"/>
+    <row r="1066" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1066" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1063" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1063" t="str">
-        <f t="shared" si="23"/>
+    <row r="1067" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1067" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1064" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1064" t="str">
-        <f t="shared" si="23"/>
+    <row r="1068" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1068" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1065" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1065" t="str">
-        <f t="shared" si="23"/>
+    <row r="1069" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1069" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1066" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1066" t="str">
-        <f t="shared" si="23"/>
+    <row r="1070" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1070" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1067" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1067" t="str">
-        <f t="shared" si="23"/>
+    <row r="1071" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="L1071" t="str">
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1068" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1068" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1069" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1069" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1070" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1070" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1071" spans="12:12" x14ac:dyDescent="0.6">
-      <c r="L1071" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1072" spans="12:12" x14ac:dyDescent="0.6">
+    <row r="1072" spans="9:14" x14ac:dyDescent="0.6">
       <c r="L1072" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1073" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1073" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1074" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1074" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1075" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1075" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1076" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1076" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1077" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1077" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1078" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1078" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1079" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1079" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1080" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1080" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1081" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1081" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1082" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1082" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1083" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1083" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1084" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1084" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1085" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1085" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1086" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1086" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1087" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1087" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1088" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1088" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1089" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1089" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1090" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1090" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1091" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1091" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1092" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1092" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1093" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1093" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1094" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1094" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1095" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1095" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1096" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1096" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1097" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1097" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1098" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1098" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1099" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1099" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1100" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1100" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1101" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1101" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1102" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1102" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1103" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1103" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1104" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1104" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1105" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1105" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1106" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1106" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1107" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1107" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1108" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1108" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1109" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1109" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1110" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1110" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1111" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1111" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1112" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1112" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1113" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1113" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1114" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1114" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1115" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1115" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1116" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1116" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1117" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1117" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1118" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1118" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1119" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1119" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1120" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1120" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1121" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1121" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1122" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1122" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1123" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1123" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1124" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1124" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="1125" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1125" t="str">
-        <f t="shared" ref="L1125:L1188" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1125:L1188" si="25">IFERROR(INDEX($R$2:$R$99,MATCH(K1125,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1126" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1126" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1127" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1127" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1128" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1128" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1129" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1129" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1130" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1130" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1131" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1131" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1132" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1132" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1133" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1133" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1134" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1134" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1135" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1135" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1136" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1136" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1137" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1137" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1138" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1138" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1139" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1139" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1140" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1140" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1141" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1141" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1142" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1142" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1143" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1143" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1144" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1144" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1145" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1145" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1146" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1146" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1147" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1147" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1148" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1148" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1149" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1149" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1150" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1150" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1151" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1151" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1152" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1152" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1153" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1153" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1154" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1154" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1155" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1155" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1156" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1156" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1157" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1157" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1158" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1158" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1159" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1159" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1160" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1160" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1161" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1161" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1162" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1162" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1163" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1163" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1164" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1164" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1165" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1165" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1166" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1166" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1167" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1167" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1168" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1168" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1169" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1169" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1170" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1170" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1171" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1171" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1172" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1172" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1173" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1173" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1174" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1174" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1175" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1175" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1176" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1176" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1177" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1177" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1178" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1178" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1179" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1179" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1180" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1180" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1181" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1181" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1182" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1182" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1183" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1183" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1184" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1184" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1185" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1185" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1186" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1186" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1187" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1187" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1188" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1188" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="1189" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1189" t="str">
-        <f t="shared" ref="L1189:L1225" si="25">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1189:L1225" si="26">IFERROR(INDEX($R$2:$R$99,MATCH(K1189,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="1190" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1190" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1191" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1191" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1192" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1192" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1193" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1193" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1194" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1194" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1195" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1195" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1196" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1196" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1197" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1197" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1198" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1198" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1199" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1199" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1200" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1200" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1201" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1201" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1202" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1202" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1203" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1203" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1204" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1204" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1205" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1205" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1206" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1206" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1207" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1207" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1208" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1208" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1209" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1209" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1210" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1210" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1211" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1211" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1212" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1212" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1213" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1213" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1214" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1214" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1215" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1215" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1216" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1216" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1217" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1217" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1218" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1218" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1219" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1219" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1220" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1220" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1221" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1221" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1222" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1222" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1223" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1223" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1224" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1224" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="1225" spans="12:12" x14ac:dyDescent="0.6">
       <c r="L1225" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47749F2F-D755-4E66-AB1B-7CD193309FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5171A5A6-8522-403C-88F7-0FCBC75D33B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{806AD57A-9F83-45E9-9DEF-1FA1D4E63FFB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5030" uniqueCount="1551">
   <si>
     <t>상대</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5292,6 +5292,30 @@
   <si>
     <t>김유나</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=l4ucM-NVjglBOtYa&amp;t=3044</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=g1GpV2LbfdoXwy5W&amp;t=3925</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=hIl6U78oe93eTRjX&amp;t=4951</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=86b5wL0o2xWZg86J&amp;t=6217</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=Vh9iW9Vl88bCmGa1&amp;t=7942</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=A4VN6kXseMdIxQqP&amp;t=8623</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=ZXt7BfGDZP6AEi2u&amp;t=9727</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MFoNvA7getQ?si=hoBHTdI1ToQ_1H4h&amp;t=10507</t>
   </si>
 </sst>
 </file>
@@ -33078,7 +33102,7 @@
         <v>1313</v>
       </c>
       <c r="L997" t="str">
-        <f t="shared" ref="L997:L1060" si="19">IFERROR(INDEX($R$2:$R$99,MATCH(K997,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L997:L1058" si="19">IFERROR(INDEX($R$2:$R$99,MATCH(K997,$Q$2:$Q$99,0)),"")</f>
         <v>Z</v>
       </c>
       <c r="M997" t="s">
@@ -34664,6 +34688,9 @@
       <c r="N1054" t="s">
         <v>1538</v>
       </c>
+      <c r="O1054" t="s">
+        <v>1543</v>
+      </c>
     </row>
     <row r="1055" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1055" s="2">
@@ -34685,6 +34712,9 @@
       <c r="N1055" t="s">
         <v>1539</v>
       </c>
+      <c r="O1055" t="s">
+        <v>1544</v>
+      </c>
     </row>
     <row r="1056" spans="1:15" x14ac:dyDescent="0.6">
       <c r="I1056" s="2">
@@ -34706,8 +34736,11 @@
       <c r="N1056" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="1057" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1056" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1057" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1057" s="2">
         <v>4</v>
       </c>
@@ -34727,8 +34760,11 @@
       <c r="N1057" t="s">
         <v>1541</v>
       </c>
-    </row>
-    <row r="1058" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1057" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1058" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1058" s="2">
         <v>5</v>
       </c>
@@ -34748,8 +34784,11 @@
       <c r="N1058" t="s">
         <v>1542</v>
       </c>
-    </row>
-    <row r="1059" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1058" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1059" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1059" s="2">
         <v>6</v>
       </c>
@@ -34769,8 +34808,11 @@
       <c r="N1059" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="1060" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1059" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1060" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1060" s="2">
         <v>7</v>
       </c>
@@ -34790,8 +34832,11 @@
       <c r="N1060" t="s">
         <v>1539</v>
       </c>
-    </row>
-    <row r="1061" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1060" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1061" spans="9:15" x14ac:dyDescent="0.6">
       <c r="I1061" s="2">
         <v>8</v>
       </c>
@@ -34811,68 +34856,71 @@
       <c r="N1061" t="s">
         <v>1538</v>
       </c>
-    </row>
-    <row r="1062" spans="9:14" x14ac:dyDescent="0.6">
+      <c r="O1061" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1062" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1062" t="str">
-        <f t="shared" ref="L1061:L1124" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1062,$Q$2:$Q$99,0)),"")</f>
+        <f t="shared" ref="L1062:L1124" si="24">IFERROR(INDEX($R$2:$R$99,MATCH(K1062,$Q$2:$Q$99,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="1063" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1063" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1063" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1064" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1064" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1064" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1065" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1065" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1065" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1066" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1066" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1066" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1067" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1067" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1067" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1068" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1068" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1068" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1069" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1069" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1069" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1070" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1070" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1070" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1071" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1071" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1071" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
-    <row r="1072" spans="9:14" x14ac:dyDescent="0.6">
+    <row r="1072" spans="9:15" x14ac:dyDescent="0.6">
       <c r="L1072" t="str">
         <f t="shared" si="24"/>
         <v/>
